--- a/105118麻醉学考研报考决策表.xlsx
+++ b/105118麻醉学考研报考决策表.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'报考决策总表'!$A$3:$N$97</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'复试与录取人数明细'!$A$3:$M$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'复试与录取人数明细'!$A$3:$N$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1428,7 +1428,9 @@
           <t>985</t>
         </is>
       </c>
-      <c r="F13" s="8" t="n"/>
+      <c r="F13" s="8" t="n">
+        <v>305</v>
+      </c>
       <c r="G13" s="8" t="n">
         <v>361</v>
       </c>
@@ -1460,7 +1462,7 @@
       </c>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>985 及强势医科大学主战场。建议初试目标 380 分以上，并同步准备 1–2 所同档备选；务必查清目标院区的【院线】而非只看校线。（该校要点：2025年录取10人均分372）</t>
+          <t>985 及强势医科大学主战场。建议初试目标 380 分以上，并同步准备 1–2 所同档备选；务必查清目标院区的【院线】而非只看校线。（该校要点：105118复试线：2024年365、2025年360、2026年305，2025年录取10人均分372）</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1612,9 @@
           <t>省属</t>
         </is>
       </c>
-      <c r="F16" s="8" t="n"/>
+      <c r="F16" s="8" t="n">
+        <v>325</v>
+      </c>
       <c r="G16" s="8" t="n">
         <v>356</v>
       </c>
@@ -1642,7 +1646,7 @@
       </c>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>985 及强势医科大学主战场。建议初试目标 380 分以上，并同步准备 1–2 所同档备选；务必查清目标院区的【院线】而非只看校线。（该校要点：2025年录取26人均分371）</t>
+          <t>985 及强势医科大学主战场。建议初试目标 380 分以上，并同步准备 1–2 所同档备选；务必查清目标院区的【院线】而非只看校线。（该校要点：105118复试线：2024年306、2025年351、2026年325，2025年录取26人均分371）</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1950,7 @@
       </c>
       <c r="N21" s="11" t="inlineStr">
         <is>
-          <t>985 及强势医科大学主战场。建议初试目标 375 分以上，并同步准备 1–2 所同档备选；务必查清目标院区的【院线】而非只看校线。（该校要点：麻醉学院332，2026年盐城临床362/淮安358/连云港352，麻醉学全国第一）</t>
+          <t>985 及强势医科大学主战场。建议初试目标 375 分以上，并同步准备 1–2 所同档备选；务必查清目标院区的【院线】而非只看校线。（该校要点：代表口径为麻醉学院：2024年321、2025年342、2026年332，其他培养单位另见年度明细）</t>
         </is>
       </c>
     </row>
@@ -2868,7 +2872,7 @@
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>东南大学</t>
+          <t>南京大学</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
@@ -2877,7 +2881,7 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="G37" s="12" t="n"/>
       <c r="H37" s="12" t="n"/>
@@ -2904,7 +2908,7 @@
       </c>
       <c r="N37" s="15" t="inlineStr">
         <is>
-          <t>省属重点医科大学主力区间，性价比最高。建议初试目标 365 分以上，基础扎实、求稳的考生首选此档。（该校要点：2026年医学院麻醉学线294）</t>
+          <t>省属重点医科大学主力区间，性价比最高。建议初试目标 365 分以上，基础扎实、求稳的考生首选此档。（该校要点：300为临床医学专业学位校级基本线，不等同于105118院线，报考前须再核对医学院细则）</t>
         </is>
       </c>
     </row>
@@ -2914,38 +2918,36 @@
       </c>
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>衡阳</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>南京大学</t>
+          <t>南华大学</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>985</t>
-        </is>
-      </c>
-      <c r="F38" s="12" t="n">
-        <v>300</v>
-      </c>
+          <t>省属</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="n"/>
       <c r="G38" s="12" t="n"/>
       <c r="H38" s="12" t="n"/>
       <c r="I38" s="12" t="n"/>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>未公布</t>
+          <t>约 5 人</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>≥ 1:1.2</t>
         </is>
       </c>
       <c r="L38" s="12" t="inlineStr">
@@ -2960,7 +2962,7 @@
       </c>
       <c r="N38" s="15" t="inlineStr">
         <is>
-          <t>省属重点医科大学主力区间，性价比最高。建议初试目标 365 分以上，基础扎实、求稳的考生首选此档。（该校要点：2026年医学院麻醉学线300）</t>
+          <t>省属重点医科大学主力区间，性价比最高。建议初试目标 365 分以上，基础扎实、求稳的考生首选此档。（该校要点：麻醉学专业排名全国第27位）</t>
         </is>
       </c>
     </row>
@@ -2970,36 +2972,38 @@
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>衡阳</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>南华大学</t>
+          <t>同济大学</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>省属</t>
-        </is>
-      </c>
-      <c r="F39" s="12" t="n"/>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>365</v>
+      </c>
       <c r="G39" s="12" t="n"/>
       <c r="H39" s="12" t="n"/>
       <c r="I39" s="12" t="n"/>
       <c r="J39" s="12" t="inlineStr">
         <is>
-          <t>约 5 人</t>
+          <t>未公布</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>≥ 1:1.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L39" s="12" t="inlineStr">
@@ -3014,7 +3018,7 @@
       </c>
       <c r="N39" s="15" t="inlineStr">
         <is>
-          <t>省属重点医科大学主力区间，性价比最高。建议初试目标 365 分以上，基础扎实、求稳的考生首选此档。（该校要点：麻醉学专业排名全国第27位）</t>
+          <t>省属重点医科大学主力区间，性价比最高。建议初试目标 365 分以上，基础扎实、求稳的考生首选此档。（该校要点：2025年专硕录取13人，2026年专硕计划13人）</t>
         </is>
       </c>
     </row>
@@ -3024,27 +3028,25 @@
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>南宁</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>同济大学</t>
+          <t>广西医科大学</t>
         </is>
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>985</t>
-        </is>
-      </c>
-      <c r="F40" s="12" t="n">
-        <v>365</v>
-      </c>
+          <t>省属</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="n"/>
       <c r="G40" s="12" t="n"/>
       <c r="H40" s="12" t="n"/>
       <c r="I40" s="12" t="n"/>
@@ -3070,7 +3072,7 @@
       </c>
       <c r="N40" s="15" t="inlineStr">
         <is>
-          <t>省属重点医科大学主力区间，性价比最高。建议初试目标 365 分以上，基础扎实、求稳的考生首选此档。（该校要点：2025年专硕录取13人，2026年专硕计划13人）</t>
+          <t>省属重点医科大学主力区间，性价比最高。建议初试目标 365 分以上，基础扎实、求稳的考生首选此档。（该校要点：麻醉学专业排名全国第16位）</t>
         </is>
       </c>
     </row>
@@ -3080,17 +3082,17 @@
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>南宁</t>
+          <t>新乡</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>广西医科大学</t>
+          <t>新乡医学院</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
@@ -3124,61 +3126,67 @@
       </c>
       <c r="N41" s="15" t="inlineStr">
         <is>
-          <t>省属重点医科大学主力区间，性价比最高。建议初试目标 365 分以上，基础扎实、求稳的考生首选此档。（该校要点：麻醉学专业排名全国第16位）</t>
+          <t>省属重点医科大学主力区间，性价比最高。建议初试目标 365 分以上，基础扎实、求稳的考生首选此档。（该校要点：麻醉学专业排名全国第33位）</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="12" t="n">
+      <c r="A42" s="16" t="n">
         <v>39</v>
       </c>
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>新乡</t>
-        </is>
-      </c>
-      <c r="D42" s="13" t="inlineStr">
-        <is>
-          <t>新乡医学院</t>
-        </is>
-      </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>广东</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>湛江</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>广东医科大学</t>
+        </is>
+      </c>
+      <c r="E42" s="16" t="inlineStr">
         <is>
           <t>省属</t>
         </is>
       </c>
-      <c r="F42" s="12" t="n"/>
-      <c r="G42" s="12" t="n"/>
-      <c r="H42" s="12" t="n"/>
-      <c r="I42" s="12" t="n"/>
-      <c r="J42" s="12" t="inlineStr">
-        <is>
-          <t>未公布</t>
-        </is>
-      </c>
-      <c r="K42" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L42" s="12" t="inlineStr">
-        <is>
-          <t>★★★☆☆</t>
-        </is>
-      </c>
-      <c r="M42" s="14" t="inlineStr">
-        <is>
-          <t>第三档 · 中坚匹配</t>
-        </is>
-      </c>
-      <c r="N42" s="15" t="inlineStr">
-        <is>
-          <t>省属重点医科大学主力区间，性价比最高。建议初试目标 365 分以上，基础扎实、求稳的考生首选此档。（该校要点：麻醉学专业排名全国第33位）</t>
+      <c r="F42" s="16" t="n"/>
+      <c r="G42" s="16" t="n">
+        <v>327</v>
+      </c>
+      <c r="H42" s="16" t="n">
+        <v>354</v>
+      </c>
+      <c r="I42" s="16" t="n">
+        <v>31</v>
+      </c>
+      <c r="J42" s="16" t="inlineStr">
+        <is>
+          <t>未公布</t>
+        </is>
+      </c>
+      <c r="K42" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L42" s="16" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="M42" s="18" t="inlineStr">
+        <is>
+          <t>第四档 · 相对稳妥</t>
+        </is>
+      </c>
+      <c r="N42" s="19" t="inlineStr">
+        <is>
+          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 360 分以上，复试正常发挥即可。（该校要点：2025年录取31人均分354）</t>
         </is>
       </c>
     </row>
@@ -3193,28 +3201,28 @@
       </c>
       <c r="C43" s="16" t="inlineStr">
         <is>
-          <t>湛江</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="D43" s="17" t="inlineStr">
         <is>
-          <t>广东医科大学</t>
+          <t>广州医科大学</t>
         </is>
       </c>
       <c r="E43" s="16" t="inlineStr">
         <is>
-          <t>省属</t>
+          <t>省属重点</t>
         </is>
       </c>
       <c r="F43" s="16" t="n"/>
       <c r="G43" s="16" t="n">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="H43" s="16" t="n">
         <v>354</v>
       </c>
       <c r="I43" s="16" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
@@ -3238,7 +3246,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 360 分以上，复试正常发挥即可。（该校要点：2025年录取31人均分354）</t>
+          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 360 分以上，复试正常发挥即可。（该校要点：2025年录取27人均分354）</t>
         </is>
       </c>
     </row>
@@ -3248,37 +3256,37 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C44" s="16" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>兰州</t>
         </is>
       </c>
       <c r="D44" s="17" t="inlineStr">
         <is>
-          <t>广州医科大学</t>
+          <t>兰州大学</t>
         </is>
       </c>
       <c r="E44" s="16" t="inlineStr">
         <is>
-          <t>省属重点</t>
+          <t>985</t>
         </is>
       </c>
       <c r="F44" s="16" t="n"/>
       <c r="G44" s="16" t="n">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="H44" s="16" t="n">
         <v>354</v>
       </c>
       <c r="I44" s="16" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>未公布</t>
+          <t>约 23 人</t>
         </is>
       </c>
       <c r="K44" s="16" t="inlineStr">
@@ -3298,7 +3306,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 360 分以上，复试正常发挥即可。（该校要点：2025年录取27人均分354）</t>
+          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 360 分以上，复试正常发挥即可。（该校要点：2025年录取16人均分354，2026年一临录取16人最低328）</t>
         </is>
       </c>
     </row>
@@ -3308,37 +3316,39 @@
       </c>
       <c r="B45" s="16" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C45" s="16" t="inlineStr">
         <is>
-          <t>兰州</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="D45" s="17" t="inlineStr">
         <is>
-          <t>兰州大学</t>
+          <t>暨南大学</t>
         </is>
       </c>
       <c r="E45" s="16" t="inlineStr">
         <is>
-          <t>985</t>
-        </is>
-      </c>
-      <c r="F45" s="16" t="n"/>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F45" s="16" t="n">
+        <v>294</v>
+      </c>
       <c r="G45" s="16" t="n">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="H45" s="16" t="n">
         <v>354</v>
       </c>
       <c r="I45" s="16" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>约 23 人</t>
+          <t>未公布</t>
         </is>
       </c>
       <c r="K45" s="16" t="inlineStr">
@@ -3358,7 +3368,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 360 分以上，复试正常发挥即可。（该校要点：2025年录取16人均分354，2026年一临录取16人最低328）</t>
+          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 360 分以上，复试正常发挥即可。（该校要点：2026年第三临床医学院294（复试比1:2），2025年录取14人均分354）</t>
         </is>
       </c>
     </row>
@@ -3368,35 +3378,31 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C46" s="16" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>齐齐哈尔</t>
         </is>
       </c>
       <c r="D46" s="17" t="inlineStr">
         <is>
-          <t>暨南大学</t>
+          <t>齐齐哈尔医学院</t>
         </is>
       </c>
       <c r="E46" s="16" t="inlineStr">
         <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="F46" s="16" t="n">
-        <v>294</v>
-      </c>
-      <c r="G46" s="16" t="n">
-        <v>323</v>
-      </c>
+          <t>省属</t>
+        </is>
+      </c>
+      <c r="F46" s="16" t="n"/>
+      <c r="G46" s="16" t="n"/>
       <c r="H46" s="16" t="n">
         <v>354</v>
       </c>
       <c r="I46" s="16" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
@@ -3420,7 +3426,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 360 分以上，复试正常发挥即可。（该校要点：2026年第三临床医学院294（复试比1:2），2025年录取14人均分354）</t>
+          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 360 分以上，复试正常发挥即可。 ⚠ 年录取≤5人，名额极少。（该校要点：2025年录取5人均分354）</t>
         </is>
       </c>
     </row>
@@ -3430,31 +3436,31 @@
       </c>
       <c r="B47" s="16" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C47" s="16" t="inlineStr">
         <is>
-          <t>齐齐哈尔</t>
+          <t>开封</t>
         </is>
       </c>
       <c r="D47" s="17" t="inlineStr">
         <is>
-          <t>齐齐哈尔医学院</t>
+          <t>河南大学</t>
         </is>
       </c>
       <c r="E47" s="16" t="inlineStr">
         <is>
-          <t>省属</t>
+          <t>双一流</t>
         </is>
       </c>
       <c r="F47" s="16" t="n"/>
       <c r="G47" s="16" t="n"/>
       <c r="H47" s="16" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="I47" s="16" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
@@ -3478,7 +3484,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 360 分以上，复试正常发挥即可。 ⚠ 年录取≤5人，名额极少。（该校要点：2025年录取5人均分354）</t>
+          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 360 分以上，复试正常发挥即可。（该校要点：2025年105118复试线323，录取18人均分353）</t>
         </is>
       </c>
     </row>
@@ -3488,31 +3494,33 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C48" s="16" t="inlineStr">
         <is>
-          <t>开封</t>
+          <t>海口</t>
         </is>
       </c>
       <c r="D48" s="17" t="inlineStr">
         <is>
-          <t>河南大学</t>
+          <t>海南医科大学</t>
         </is>
       </c>
       <c r="E48" s="16" t="inlineStr">
         <is>
-          <t>双一流</t>
+          <t>省属</t>
         </is>
       </c>
       <c r="F48" s="16" t="n"/>
-      <c r="G48" s="16" t="n"/>
+      <c r="G48" s="16" t="n">
+        <v>338</v>
+      </c>
       <c r="H48" s="16" t="n">
         <v>353</v>
       </c>
       <c r="I48" s="16" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
@@ -3536,7 +3544,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 360 分以上，复试正常发挥即可。（该校要点：2025年录取18人均分353）</t>
+          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 360 分以上，复试正常发挥即可。（该校要点：2025年录取9人均分353）</t>
         </is>
       </c>
     </row>
@@ -3546,33 +3554,33 @@
       </c>
       <c r="B49" s="16" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C49" s="16" t="inlineStr">
         <is>
-          <t>海口</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D49" s="17" t="inlineStr">
         <is>
-          <t>海南医科大学</t>
+          <t>海军军医大学</t>
         </is>
       </c>
       <c r="E49" s="16" t="inlineStr">
         <is>
-          <t>省属</t>
+          <t>211/军队</t>
         </is>
       </c>
       <c r="F49" s="16" t="n"/>
       <c r="G49" s="16" t="n">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="H49" s="16" t="n">
         <v>353</v>
       </c>
       <c r="I49" s="16" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
@@ -3596,7 +3604,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 360 分以上，复试正常发挥即可。（该校要点：2025年录取9人均分353）</t>
+          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 360 分以上，复试正常发挥即可。 ⚠ 年录取≤5人，名额极少。（该校要点：2025年录取1人353分）</t>
         </is>
       </c>
     </row>
@@ -3606,33 +3614,31 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C50" s="16" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>青岛</t>
         </is>
       </c>
       <c r="D50" s="17" t="inlineStr">
         <is>
-          <t>海军军医大学</t>
+          <t>青岛大学</t>
         </is>
       </c>
       <c r="E50" s="16" t="inlineStr">
         <is>
-          <t>211/军队</t>
+          <t>省属重点</t>
         </is>
       </c>
       <c r="F50" s="16" t="n"/>
-      <c r="G50" s="16" t="n">
-        <v>353</v>
-      </c>
+      <c r="G50" s="16" t="n"/>
       <c r="H50" s="16" t="n">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I50" s="16" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
@@ -3656,7 +3662,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 360 分以上，复试正常发挥即可。 ⚠ 年录取≤5人，名额极少。（该校要点：2025年录取1人353分）</t>
+          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 360 分以上，复试正常发挥即可。（该校要点：2025年录取22人均分352）</t>
         </is>
       </c>
     </row>
@@ -3666,31 +3672,33 @@
       </c>
       <c r="B51" s="16" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C51" s="16" t="inlineStr">
         <is>
-          <t>青岛</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="D51" s="17" t="inlineStr">
         <is>
-          <t>青岛大学</t>
+          <t>武汉大学</t>
         </is>
       </c>
       <c r="E51" s="16" t="inlineStr">
         <is>
-          <t>省属重点</t>
+          <t>985</t>
         </is>
       </c>
       <c r="F51" s="16" t="n"/>
-      <c r="G51" s="16" t="n"/>
+      <c r="G51" s="16" t="n">
+        <v>336</v>
+      </c>
       <c r="H51" s="16" t="n">
         <v>352</v>
       </c>
       <c r="I51" s="16" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
@@ -3714,7 +3722,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 360 分以上，复试正常发挥即可。（该校要点：2025年录取22人均分352）</t>
+          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 360 分以上，复试正常发挥即可。（该校要点：2025年录取19人均分352）</t>
         </is>
       </c>
     </row>
@@ -3724,33 +3732,35 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C52" s="16" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>温州</t>
         </is>
       </c>
       <c r="D52" s="17" t="inlineStr">
         <is>
-          <t>武汉大学</t>
+          <t>温州医科大学</t>
         </is>
       </c>
       <c r="E52" s="16" t="inlineStr">
         <is>
-          <t>985</t>
-        </is>
-      </c>
-      <c r="F52" s="16" t="n"/>
+          <t>省属重点</t>
+        </is>
+      </c>
+      <c r="F52" s="16" t="n">
+        <v>350</v>
+      </c>
       <c r="G52" s="16" t="n">
-        <v>336</v>
+        <v>295</v>
       </c>
       <c r="H52" s="16" t="n">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="I52" s="16" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
@@ -3774,7 +3784,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 360 分以上，复试正常发挥即可。（该校要点：2025年录取19人均分352）</t>
+          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 360 分以上，复试正常发挥即可。 ⚠ 2026年院线大幅上调。（该校要点：105118复试线：2024年345、2025年执行A区线293、2026年350，2025年全校各培养单位合计录取49人）</t>
         </is>
       </c>
     </row>
@@ -3784,17 +3794,17 @@
       </c>
       <c r="B53" s="16" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C53" s="16" t="inlineStr">
         <is>
-          <t>温州</t>
+          <t>太原</t>
         </is>
       </c>
       <c r="D53" s="17" t="inlineStr">
         <is>
-          <t>温州医科大学</t>
+          <t>山西医科大学</t>
         </is>
       </c>
       <c r="E53" s="16" t="inlineStr">
@@ -3802,26 +3812,24 @@
           <t>省属重点</t>
         </is>
       </c>
-      <c r="F53" s="16" t="n">
-        <v>350</v>
-      </c>
+      <c r="F53" s="16" t="n"/>
       <c r="G53" s="16" t="n">
-        <v>295</v>
+        <v>334</v>
       </c>
       <c r="H53" s="16" t="n">
         <v>351</v>
       </c>
       <c r="I53" s="16" t="n">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>未公布</t>
+          <t>约 34 人</t>
         </is>
       </c>
       <c r="K53" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1:1.3</t>
         </is>
       </c>
       <c r="L53" s="16" t="inlineStr">
@@ -3836,7 +3844,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 360 分以上，复试正常发挥即可。（该校要点：2024年录取9人最低349最高420均分373，2025年录取47人均分351）</t>
+          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 360 分以上，复试正常发挥即可。（该校要点：2024年首次招生343，2025年录取31人均分351）</t>
         </is>
       </c>
     </row>
@@ -3846,42 +3854,42 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C54" s="16" t="inlineStr">
         <is>
-          <t>太原</t>
+          <t>佳木斯</t>
         </is>
       </c>
       <c r="D54" s="17" t="inlineStr">
         <is>
-          <t>山西医科大学</t>
+          <t>佳木斯大学</t>
         </is>
       </c>
       <c r="E54" s="16" t="inlineStr">
         <is>
-          <t>省属重点</t>
+          <t>省属</t>
         </is>
       </c>
       <c r="F54" s="16" t="n"/>
       <c r="G54" s="16" t="n">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="H54" s="16" t="n">
         <v>351</v>
       </c>
       <c r="I54" s="16" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>约 34 人</t>
+          <t>未公布</t>
         </is>
       </c>
       <c r="K54" s="16" t="inlineStr">
         <is>
-          <t>1:1.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L54" s="16" t="inlineStr">
@@ -3896,7 +3904,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 360 分以上，复试正常发挥即可。（该校要点：2024年首次招生343，2025年录取31人均分351）</t>
+          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 360 分以上，复试正常发挥即可。（该校要点：2025年录取约9人均分356（原表数据不完整））</t>
         </is>
       </c>
     </row>
@@ -3906,33 +3914,31 @@
       </c>
       <c r="B55" s="16" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C55" s="16" t="inlineStr">
         <is>
-          <t>佳木斯</t>
+          <t>兰州</t>
         </is>
       </c>
       <c r="D55" s="17" t="inlineStr">
         <is>
-          <t>佳木斯大学</t>
+          <t>西北民族大学</t>
         </is>
       </c>
       <c r="E55" s="16" t="inlineStr">
         <is>
-          <t>省属</t>
+          <t>B区省属</t>
         </is>
       </c>
       <c r="F55" s="16" t="n"/>
-      <c r="G55" s="16" t="n">
-        <v>356</v>
-      </c>
+      <c r="G55" s="16" t="n"/>
       <c r="H55" s="16" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="I55" s="16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
@@ -3956,7 +3962,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 360 分以上，复试正常发挥即可。（该校要点：2025年录取约9人均分356（原表数据不完整））</t>
+          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 360 分以上，复试正常发挥即可。 ⚠ 年录取≤5人，名额极少。（该校要点：—）</t>
         </is>
       </c>
     </row>
@@ -3966,31 +3972,35 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C56" s="16" t="inlineStr">
         <is>
-          <t>兰州</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="D56" s="17" t="inlineStr">
         <is>
-          <t>西北民族大学</t>
+          <t>昆明医科大学</t>
         </is>
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
-          <t>B区省属</t>
-        </is>
-      </c>
-      <c r="F56" s="16" t="n"/>
-      <c r="G56" s="16" t="n"/>
+          <t>省属</t>
+        </is>
+      </c>
+      <c r="F56" s="16" t="n">
+        <v>315</v>
+      </c>
+      <c r="G56" s="16" t="n">
+        <v>305</v>
+      </c>
       <c r="H56" s="16" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I56" s="16" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
@@ -4014,7 +4024,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 360 分以上，复试正常发挥即可。 ⚠ 年录取≤5人，名额极少。（该校要点：—）</t>
+          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 355 分以上，复试正常发挥即可。 ⚠ 2026年院线大幅上调。（该校要点：2025年录取42人均分349）</t>
         </is>
       </c>
     </row>
@@ -4024,17 +4034,17 @@
       </c>
       <c r="B57" s="16" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C57" s="16" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>蚌埠</t>
         </is>
       </c>
       <c r="D57" s="17" t="inlineStr">
         <is>
-          <t>昆明医科大学</t>
+          <t>蚌埠医科大学</t>
         </is>
       </c>
       <c r="E57" s="16" t="inlineStr">
@@ -4042,17 +4052,15 @@
           <t>省属</t>
         </is>
       </c>
-      <c r="F57" s="16" t="n">
-        <v>315</v>
-      </c>
+      <c r="F57" s="16" t="n"/>
       <c r="G57" s="16" t="n">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="H57" s="16" t="n">
         <v>349</v>
       </c>
       <c r="I57" s="16" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
@@ -4076,7 +4084,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 355 分以上，复试正常发挥即可。 ⚠ 2026年院线大幅上调。（该校要点：2025年录取42人均分349）</t>
+          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 355 分以上，复试正常发挥即可。（该校要点：2025年录取29人均分349，2026年录取14人均分330）</t>
         </is>
       </c>
     </row>
@@ -4086,17 +4094,17 @@
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C58" s="16" t="inlineStr">
         <is>
-          <t>蚌埠</t>
+          <t>贵阳</t>
         </is>
       </c>
       <c r="D58" s="17" t="inlineStr">
         <is>
-          <t>蚌埠医科大学</t>
+          <t>贵州医科大学</t>
         </is>
       </c>
       <c r="E58" s="16" t="inlineStr">
@@ -4104,15 +4112,17 @@
           <t>省属</t>
         </is>
       </c>
-      <c r="F58" s="16" t="n"/>
+      <c r="F58" s="16" t="n">
+        <v>319</v>
+      </c>
       <c r="G58" s="16" t="n">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="H58" s="16" t="n">
         <v>349</v>
       </c>
       <c r="I58" s="16" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
@@ -4136,7 +4146,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 355 分以上，复试正常发挥即可。（该校要点：2025年录取29人均分349，2026年录取14人均分330）</t>
+          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 355 分以上，复试正常发挥即可。 ⚠ 2026年院线大幅上调。（该校要点：2025年录取21人均分349，2026年疼痛方向录取6人均分338）</t>
         </is>
       </c>
     </row>
@@ -4146,17 +4156,17 @@
       </c>
       <c r="B59" s="16" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>四川</t>
         </is>
       </c>
       <c r="C59" s="16" t="inlineStr">
         <is>
-          <t>贵阳</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="D59" s="17" t="inlineStr">
         <is>
-          <t>贵州医科大学</t>
+          <t>成都医学院</t>
         </is>
       </c>
       <c r="E59" s="16" t="inlineStr">
@@ -4164,17 +4174,13 @@
           <t>省属</t>
         </is>
       </c>
-      <c r="F59" s="16" t="n">
-        <v>319</v>
-      </c>
-      <c r="G59" s="16" t="n">
-        <v>319</v>
-      </c>
+      <c r="F59" s="16" t="n"/>
+      <c r="G59" s="16" t="n"/>
       <c r="H59" s="16" t="n">
         <v>349</v>
       </c>
       <c r="I59" s="16" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
@@ -4198,7 +4204,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 355 分以上，复试正常发挥即可。 ⚠ 2026年院线大幅上调。（该校要点：2025年录取21人均分349，2026年疼痛方向录取6人均分338）</t>
+          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 355 分以上，复试正常发挥即可。（该校要点：105118复试线：2024年332、2025年320）</t>
         </is>
       </c>
     </row>
@@ -4208,17 +4214,17 @@
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>四川</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C60" s="16" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>绍兴</t>
         </is>
       </c>
       <c r="D60" s="17" t="inlineStr">
         <is>
-          <t>成都医学院</t>
+          <t>绍兴文理学院</t>
         </is>
       </c>
       <c r="E60" s="16" t="inlineStr">
@@ -4227,12 +4233,14 @@
         </is>
       </c>
       <c r="F60" s="16" t="n"/>
-      <c r="G60" s="16" t="n"/>
+      <c r="G60" s="16" t="n">
+        <v>335</v>
+      </c>
       <c r="H60" s="16" t="n">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="I60" s="16" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
@@ -4256,7 +4264,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 355 分以上，复试正常发挥即可。（该校要点：2024年拟录取14人最低332）</t>
+          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 355 分以上，复试正常发挥即可。 ⚠ 年录取≤5人，名额极少。（该校要点：2024年录取6人均分334.8，2026年录取5人均分335.6）</t>
         </is>
       </c>
     </row>
@@ -4266,17 +4274,17 @@
       </c>
       <c r="B61" s="16" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C61" s="16" t="inlineStr">
         <is>
-          <t>绍兴</t>
+          <t>镇江</t>
         </is>
       </c>
       <c r="D61" s="17" t="inlineStr">
         <is>
-          <t>绍兴文理学院</t>
+          <t>江苏大学</t>
         </is>
       </c>
       <c r="E61" s="16" t="inlineStr">
@@ -4284,15 +4292,15 @@
           <t>省属</t>
         </is>
       </c>
-      <c r="F61" s="16" t="n"/>
-      <c r="G61" s="16" t="n">
-        <v>335</v>
-      </c>
+      <c r="F61" s="16" t="n">
+        <v>294</v>
+      </c>
+      <c r="G61" s="16" t="n"/>
       <c r="H61" s="16" t="n">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="I61" s="16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
@@ -4316,7 +4324,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 355 分以上，复试正常发挥即可。 ⚠ 年录取≤5人，名额极少。（该校要点：2024年录取6人均分334.8，2026年录取5人均分335.6）</t>
+          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 355 分以上，复试正常发挥即可。（该校要点：2026年招生7人，2025年录取8人均分345）</t>
         </is>
       </c>
     </row>
@@ -4326,17 +4334,17 @@
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>黑龙江</t>
         </is>
       </c>
       <c r="C62" s="16" t="inlineStr">
         <is>
-          <t>镇江</t>
+          <t>牡丹江</t>
         </is>
       </c>
       <c r="D62" s="17" t="inlineStr">
         <is>
-          <t>江苏大学</t>
+          <t>牡丹江医科大学</t>
         </is>
       </c>
       <c r="E62" s="16" t="inlineStr">
@@ -4345,23 +4353,21 @@
         </is>
       </c>
       <c r="F62" s="16" t="n">
-        <v>294</v>
+        <v>322</v>
       </c>
       <c r="G62" s="16" t="n"/>
-      <c r="H62" s="16" t="n">
-        <v>345</v>
-      </c>
+      <c r="H62" s="16" t="n"/>
       <c r="I62" s="16" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>未公布</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K62" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>≥ 1:1.2</t>
         </is>
       </c>
       <c r="L62" s="16" t="inlineStr">
@@ -4376,7 +4382,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 355 分以上，复试正常发挥即可。（该校要点：2026年招生7人，2025年录取8人均分345）</t>
+          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 355 分以上，复试正常发挥即可。 ⚠ 2026年院线大幅上调。（该校要点：2026年麻醉学（附属红旗医院基地）322分）</t>
         </is>
       </c>
     </row>
@@ -4386,40 +4392,38 @@
       </c>
       <c r="B63" s="16" t="inlineStr">
         <is>
-          <t>黑龙江</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C63" s="16" t="inlineStr">
         <is>
-          <t>牡丹江</t>
+          <t>大连</t>
         </is>
       </c>
       <c r="D63" s="17" t="inlineStr">
         <is>
-          <t>牡丹江医科大学</t>
+          <t>大连理工大学</t>
         </is>
       </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
-          <t>省属</t>
+          <t>985</t>
         </is>
       </c>
       <c r="F63" s="16" t="n">
-        <v>322</v>
+        <v>300</v>
       </c>
       <c r="G63" s="16" t="n"/>
       <c r="H63" s="16" t="n"/>
-      <c r="I63" s="16" t="n">
-        <v>18</v>
-      </c>
+      <c r="I63" s="16" t="n"/>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>未公布</t>
         </is>
       </c>
       <c r="K63" s="16" t="inlineStr">
         <is>
-          <t>≥ 1:1.2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L63" s="16" t="inlineStr">
@@ -4434,63 +4438,67 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 355 分以上，复试正常发挥即可。 ⚠ 2026年院线大幅上调。（该校要点：2026年麻醉学（附属红旗医院基地）322分）</t>
+          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 355 分以上，复试正常发挥即可。 ⚠ 推免占比高，统考名额有限。（该校要点：2026年105118复试线300，统考招生1人）</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="16" t="n">
+      <c r="A64" s="20" t="n">
         <v>61</v>
       </c>
-      <c r="B64" s="16" t="inlineStr">
-        <is>
-          <t>辽宁</t>
-        </is>
-      </c>
-      <c r="C64" s="16" t="inlineStr">
-        <is>
-          <t>大连</t>
-        </is>
-      </c>
-      <c r="D64" s="17" t="inlineStr">
-        <is>
-          <t>大连理工大学</t>
-        </is>
-      </c>
-      <c r="E64" s="16" t="inlineStr">
-        <is>
-          <t>985</t>
-        </is>
-      </c>
-      <c r="F64" s="16" t="n">
-        <v>300</v>
-      </c>
-      <c r="G64" s="16" t="n"/>
-      <c r="H64" s="16" t="n"/>
-      <c r="I64" s="16" t="n"/>
-      <c r="J64" s="16" t="inlineStr">
-        <is>
-          <t>未公布</t>
-        </is>
-      </c>
-      <c r="K64" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L64" s="16" t="inlineStr">
-        <is>
-          <t>★★☆☆☆</t>
-        </is>
-      </c>
-      <c r="M64" s="18" t="inlineStr">
-        <is>
-          <t>第四档 · 相对稳妥</t>
-        </is>
-      </c>
-      <c r="N64" s="19" t="inlineStr">
-        <is>
-          <t>上岸概率明显提升，适合求稳或有明确地域规划的考生。建议初试目标 355 分以上，复试正常发挥即可。 ⚠ 推免占比高，统考名额有限。（该校要点：2026年麻醉学统考招生1人）</t>
+      <c r="B64" s="20" t="inlineStr">
+        <is>
+          <t>山东</t>
+        </is>
+      </c>
+      <c r="C64" s="20" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="D64" s="21" t="inlineStr">
+        <is>
+          <t>山东第一医科大学</t>
+        </is>
+      </c>
+      <c r="E64" s="20" t="inlineStr">
+        <is>
+          <t>省属</t>
+        </is>
+      </c>
+      <c r="F64" s="20" t="n"/>
+      <c r="G64" s="20" t="n">
+        <v>297</v>
+      </c>
+      <c r="H64" s="20" t="n">
+        <v>344</v>
+      </c>
+      <c r="I64" s="20" t="n">
+        <v>28</v>
+      </c>
+      <c r="J64" s="20" t="inlineStr">
+        <is>
+          <t>未公布</t>
+        </is>
+      </c>
+      <c r="K64" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L64" s="20" t="inlineStr">
+        <is>
+          <t>★☆☆☆☆</t>
+        </is>
+      </c>
+      <c r="M64" s="22" t="inlineStr">
+        <is>
+          <t>第五档 · 友好保底</t>
+        </is>
+      </c>
+      <c r="N64" s="23" t="inlineStr">
+        <is>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 350 分以上，适合压线求稳或求保底。（该校要点：2025年录取28人均分344）</t>
         </is>
       </c>
     </row>
@@ -4500,17 +4508,17 @@
       </c>
       <c r="B65" s="20" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C65" s="20" t="inlineStr">
         <is>
-          <t>济南</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="D65" s="21" t="inlineStr">
         <is>
-          <t>山东第一医科大学</t>
+          <t>杭州师范大学</t>
         </is>
       </c>
       <c r="E65" s="20" t="inlineStr">
@@ -4519,14 +4527,12 @@
         </is>
       </c>
       <c r="F65" s="20" t="n"/>
-      <c r="G65" s="20" t="n">
-        <v>297</v>
-      </c>
+      <c r="G65" s="20" t="n"/>
       <c r="H65" s="20" t="n">
         <v>344</v>
       </c>
       <c r="I65" s="20" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="J65" s="20" t="inlineStr">
         <is>
@@ -4550,7 +4556,7 @@
       </c>
       <c r="N65" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 350 分以上，适合压线求稳或求保底。（该校要点：2025年录取28人均分344）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 350 分以上，适合压线求稳或求保底。 ⚠ 年录取≤5人，名额极少。（该校要点：2026年录取2人最低359，2025年录取3人均分344）</t>
         </is>
       </c>
     </row>
@@ -4560,17 +4566,17 @@
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>贵州</t>
         </is>
       </c>
       <c r="C66" s="20" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>遵义</t>
         </is>
       </c>
       <c r="D66" s="21" t="inlineStr">
         <is>
-          <t>杭州师范大学</t>
+          <t>遵义医科大学</t>
         </is>
       </c>
       <c r="E66" s="20" t="inlineStr">
@@ -4579,12 +4585,14 @@
         </is>
       </c>
       <c r="F66" s="20" t="n"/>
-      <c r="G66" s="20" t="n"/>
+      <c r="G66" s="20" t="n">
+        <v>310</v>
+      </c>
       <c r="H66" s="20" t="n">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I66" s="20" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="J66" s="20" t="inlineStr">
         <is>
@@ -4608,7 +4616,7 @@
       </c>
       <c r="N66" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 350 分以上，适合压线求稳或求保底。 ⚠ 年录取≤5人，名额极少。（该校要点：2026年录取2人最低359，2025年录取3人均分344）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 350 分以上，适合压线求稳或求保底。（该校要点：2025年录取24人均分343）</t>
         </is>
       </c>
     </row>
@@ -4618,17 +4626,17 @@
       </c>
       <c r="B67" s="20" t="inlineStr">
         <is>
-          <t>贵州</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C67" s="20" t="inlineStr">
         <is>
-          <t>遵义</t>
+          <t>沈阳</t>
         </is>
       </c>
       <c r="D67" s="21" t="inlineStr">
         <is>
-          <t>遵义医科大学</t>
+          <t>沈阳医学院</t>
         </is>
       </c>
       <c r="E67" s="20" t="inlineStr">
@@ -4637,14 +4645,12 @@
         </is>
       </c>
       <c r="F67" s="20" t="n"/>
-      <c r="G67" s="20" t="n">
-        <v>310</v>
-      </c>
+      <c r="G67" s="20" t="n"/>
       <c r="H67" s="20" t="n">
         <v>343</v>
       </c>
       <c r="I67" s="20" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="J67" s="20" t="inlineStr">
         <is>
@@ -4668,7 +4674,7 @@
       </c>
       <c r="N67" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 350 分以上，适合压线求稳或求保底。（该校要点：2025年录取24人均分343）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 350 分以上，适合压线求稳或求保底。（该校要点：—）</t>
         </is>
       </c>
     </row>
@@ -4678,17 +4684,17 @@
       </c>
       <c r="B68" s="20" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C68" s="20" t="inlineStr">
         <is>
-          <t>沈阳</t>
+          <t>潍坊</t>
         </is>
       </c>
       <c r="D68" s="21" t="inlineStr">
         <is>
-          <t>沈阳医学院</t>
+          <t>山东第二医科大学</t>
         </is>
       </c>
       <c r="E68" s="20" t="inlineStr">
@@ -4697,12 +4703,14 @@
         </is>
       </c>
       <c r="F68" s="20" t="n"/>
-      <c r="G68" s="20" t="n"/>
+      <c r="G68" s="20" t="n">
+        <v>326</v>
+      </c>
       <c r="H68" s="20" t="n">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I68" s="20" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="J68" s="20" t="inlineStr">
         <is>
@@ -4726,7 +4734,7 @@
       </c>
       <c r="N68" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 350 分以上，适合压线求稳或求保底。（该校要点：—）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 350 分以上，适合压线求稳或求保底。（该校要点：2025年录取30人均分342）</t>
         </is>
       </c>
     </row>
@@ -4736,42 +4744,42 @@
       </c>
       <c r="B69" s="20" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C69" s="20" t="inlineStr">
         <is>
-          <t>潍坊</t>
+          <t>银川</t>
         </is>
       </c>
       <c r="D69" s="21" t="inlineStr">
         <is>
-          <t>山东第二医科大学</t>
+          <t>宁夏医科大学</t>
         </is>
       </c>
       <c r="E69" s="20" t="inlineStr">
         <is>
-          <t>省属</t>
+          <t>B区省属</t>
         </is>
       </c>
       <c r="F69" s="20" t="n"/>
       <c r="G69" s="20" t="n">
-        <v>326</v>
+        <v>294</v>
       </c>
       <c r="H69" s="20" t="n">
         <v>342</v>
       </c>
       <c r="I69" s="20" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J69" s="20" t="inlineStr">
         <is>
-          <t>未公布</t>
+          <t>18 – 20 人</t>
         </is>
       </c>
       <c r="K69" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>约 1:1.3</t>
         </is>
       </c>
       <c r="L69" s="20" t="inlineStr">
@@ -4786,7 +4794,7 @@
       </c>
       <c r="N69" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 350 分以上，适合压线求稳或求保底。（该校要点：2025年录取30人均分342）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 350 分以上，适合压线求稳或求保底。（该校要点：2025年录取20人均分342，2026年第三临床15人均分342）</t>
         </is>
       </c>
     </row>
@@ -4796,42 +4804,42 @@
       </c>
       <c r="B70" s="20" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>江西</t>
         </is>
       </c>
       <c r="C70" s="20" t="inlineStr">
         <is>
-          <t>银川</t>
+          <t>赣州</t>
         </is>
       </c>
       <c r="D70" s="21" t="inlineStr">
         <is>
-          <t>宁夏医科大学</t>
+          <t>赣南医科大学</t>
         </is>
       </c>
       <c r="E70" s="20" t="inlineStr">
         <is>
-          <t>B区省属</t>
+          <t>省属</t>
         </is>
       </c>
       <c r="F70" s="20" t="n"/>
       <c r="G70" s="20" t="n">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="H70" s="20" t="n">
         <v>342</v>
       </c>
       <c r="I70" s="20" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J70" s="20" t="inlineStr">
         <is>
-          <t>18 – 20 人</t>
+          <t>未公布</t>
         </is>
       </c>
       <c r="K70" s="20" t="inlineStr">
         <is>
-          <t>约 1:1.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L70" s="20" t="inlineStr">
@@ -4846,7 +4854,7 @@
       </c>
       <c r="N70" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 350 分以上，适合压线求稳或求保底。（该校要点：2025年录取20人均分342，2026年第三临床15人均分342）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 350 分以上，适合压线求稳或求保底。（该校要点：2025年录取14人均分342）</t>
         </is>
       </c>
     </row>
@@ -4856,17 +4864,17 @@
       </c>
       <c r="B71" s="20" t="inlineStr">
         <is>
-          <t>江西</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C71" s="20" t="inlineStr">
         <is>
-          <t>赣州</t>
+          <t>延安</t>
         </is>
       </c>
       <c r="D71" s="21" t="inlineStr">
         <is>
-          <t>赣南医科大学</t>
+          <t>延安大学</t>
         </is>
       </c>
       <c r="E71" s="20" t="inlineStr">
@@ -4874,15 +4882,15 @@
           <t>省属</t>
         </is>
       </c>
-      <c r="F71" s="20" t="n"/>
-      <c r="G71" s="20" t="n">
-        <v>303</v>
-      </c>
+      <c r="F71" s="20" t="n">
+        <v>307</v>
+      </c>
+      <c r="G71" s="20" t="n"/>
       <c r="H71" s="20" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I71" s="20" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="J71" s="20" t="inlineStr">
         <is>
@@ -4906,7 +4914,7 @@
       </c>
       <c r="N71" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 350 分以上，适合压线求稳或求保底。（该校要点：2025年录取14人均分342）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 350 分以上，适合压线求稳或求保底。（该校要点：105118复试线：2024年304、2025年325、2026年307）</t>
         </is>
       </c>
     </row>
@@ -4916,17 +4924,17 @@
       </c>
       <c r="B72" s="20" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C72" s="20" t="inlineStr">
         <is>
-          <t>延安</t>
+          <t>南通</t>
         </is>
       </c>
       <c r="D72" s="21" t="inlineStr">
         <is>
-          <t>延安大学</t>
+          <t>南通大学</t>
         </is>
       </c>
       <c r="E72" s="20" t="inlineStr">
@@ -4934,15 +4942,15 @@
           <t>省属</t>
         </is>
       </c>
-      <c r="F72" s="20" t="n">
-        <v>307</v>
-      </c>
-      <c r="G72" s="20" t="n"/>
+      <c r="F72" s="20" t="n"/>
+      <c r="G72" s="20" t="n">
+        <v>301</v>
+      </c>
       <c r="H72" s="20" t="n">
         <v>341</v>
       </c>
       <c r="I72" s="20" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J72" s="20" t="inlineStr">
         <is>
@@ -4966,7 +4974,7 @@
       </c>
       <c r="N72" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 350 分以上，适合压线求稳或求保底。（该校要点：2026年延安医学院麻醉学307分）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 350 分以上，适合压线求稳或求保底。（该校要点：2025年录取19人均分341）</t>
         </is>
       </c>
     </row>
@@ -4976,17 +4984,17 @@
       </c>
       <c r="B73" s="20" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C73" s="20" t="inlineStr">
         <is>
-          <t>南通</t>
+          <t>西安</t>
         </is>
       </c>
       <c r="D73" s="21" t="inlineStr">
         <is>
-          <t>南通大学</t>
+          <t>西安医学院</t>
         </is>
       </c>
       <c r="E73" s="20" t="inlineStr">
@@ -4996,13 +5004,13 @@
       </c>
       <c r="F73" s="20" t="n"/>
       <c r="G73" s="20" t="n">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="H73" s="20" t="n">
         <v>341</v>
       </c>
       <c r="I73" s="20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J73" s="20" t="inlineStr">
         <is>
@@ -5026,7 +5034,7 @@
       </c>
       <c r="N73" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 350 分以上，适合压线求稳或求保底。（该校要点：2025年录取19人均分341）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 350 分以上，适合压线求稳或求保底。（该校要点：2025年录取18人均分341）</t>
         </is>
       </c>
     </row>
@@ -5036,33 +5044,33 @@
       </c>
       <c r="B74" s="20" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C74" s="20" t="inlineStr">
         <is>
-          <t>西安</t>
+          <t>大连</t>
         </is>
       </c>
       <c r="D74" s="21" t="inlineStr">
         <is>
-          <t>西安医学院</t>
+          <t>大连医科大学</t>
         </is>
       </c>
       <c r="E74" s="20" t="inlineStr">
         <is>
-          <t>省属</t>
+          <t>省属重点</t>
         </is>
       </c>
       <c r="F74" s="20" t="n"/>
       <c r="G74" s="20" t="n">
-        <v>322</v>
+        <v>298</v>
       </c>
       <c r="H74" s="20" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I74" s="20" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="J74" s="20" t="inlineStr">
         <is>
@@ -5086,7 +5094,7 @@
       </c>
       <c r="N74" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 350 分以上，适合压线求稳或求保底。（该校要点：2025年录取18人均分341）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 350 分以上，适合压线求稳或求保底。（该校要点：2025年录取48人均分340）</t>
         </is>
       </c>
     </row>
@@ -5096,33 +5104,31 @@
       </c>
       <c r="B75" s="20" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C75" s="20" t="inlineStr">
         <is>
-          <t>大连</t>
+          <t>大理</t>
         </is>
       </c>
       <c r="D75" s="21" t="inlineStr">
         <is>
-          <t>大连医科大学</t>
+          <t>大理大学</t>
         </is>
       </c>
       <c r="E75" s="20" t="inlineStr">
         <is>
-          <t>省属重点</t>
+          <t>B区省属</t>
         </is>
       </c>
       <c r="F75" s="20" t="n"/>
-      <c r="G75" s="20" t="n">
-        <v>298</v>
-      </c>
+      <c r="G75" s="20" t="n"/>
       <c r="H75" s="20" t="n">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I75" s="20" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="J75" s="20" t="inlineStr">
         <is>
@@ -5146,7 +5152,7 @@
       </c>
       <c r="N75" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 350 分以上，适合压线求稳或求保底。（该校要点：2025年录取48人均分340）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 345 分以上，适合压线求稳或求保底。（该校要点：2025年录取15人均分339）</t>
         </is>
       </c>
     </row>
@@ -5156,31 +5162,33 @@
       </c>
       <c r="B76" s="20" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C76" s="20" t="inlineStr">
         <is>
-          <t>大理</t>
+          <t>承德</t>
         </is>
       </c>
       <c r="D76" s="21" t="inlineStr">
         <is>
-          <t>大理大学</t>
+          <t>承德医学院</t>
         </is>
       </c>
       <c r="E76" s="20" t="inlineStr">
         <is>
-          <t>B区省属</t>
+          <t>省属</t>
         </is>
       </c>
       <c r="F76" s="20" t="n"/>
-      <c r="G76" s="20" t="n"/>
+      <c r="G76" s="20" t="n">
+        <v>305</v>
+      </c>
       <c r="H76" s="20" t="n">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="I76" s="20" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J76" s="20" t="inlineStr">
         <is>
@@ -5204,7 +5212,7 @@
       </c>
       <c r="N76" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 345 分以上，适合压线求稳或求保底。（该校要点：2025年录取15人均分339）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 345 分以上，适合压线求稳或求保底。（该校要点：2025年录取约10人均分335（循国家A线））</t>
         </is>
       </c>
     </row>
@@ -5214,33 +5222,35 @@
       </c>
       <c r="B77" s="20" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C77" s="20" t="inlineStr">
         <is>
-          <t>承德</t>
+          <t>无锡</t>
         </is>
       </c>
       <c r="D77" s="21" t="inlineStr">
         <is>
-          <t>承德医学院</t>
+          <t>江南大学</t>
         </is>
       </c>
       <c r="E77" s="20" t="inlineStr">
         <is>
-          <t>省属</t>
-        </is>
-      </c>
-      <c r="F77" s="20" t="n"/>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F77" s="20" t="n">
+        <v>335</v>
+      </c>
       <c r="G77" s="20" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="H77" s="20" t="n">
         <v>337</v>
       </c>
       <c r="I77" s="20" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J77" s="20" t="inlineStr">
         <is>
@@ -5264,7 +5274,7 @@
       </c>
       <c r="N77" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 345 分以上，适合压线求稳或求保底。（该校要点：2025年录取约10人均分335（循国家A线））</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 345 分以上，适合压线求稳或求保底。 ⚠ 2026年院线大幅上调。（该校要点：105118复试线：2024年319、2025年310、2026年335，2025年录取9人均分337）</t>
         </is>
       </c>
     </row>
@@ -5274,17 +5284,17 @@
       </c>
       <c r="B78" s="20" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>吉林</t>
         </is>
       </c>
       <c r="C78" s="20" t="inlineStr">
         <is>
-          <t>无锡</t>
+          <t>延吉</t>
         </is>
       </c>
       <c r="D78" s="21" t="inlineStr">
         <is>
-          <t>江南大学</t>
+          <t>延边大学</t>
         </is>
       </c>
       <c r="E78" s="20" t="inlineStr">
@@ -5292,17 +5302,15 @@
           <t>211</t>
         </is>
       </c>
-      <c r="F78" s="20" t="n">
-        <v>335</v>
-      </c>
+      <c r="F78" s="20" t="n"/>
       <c r="G78" s="20" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H78" s="20" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="I78" s="20" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="J78" s="20" t="inlineStr">
         <is>
@@ -5326,7 +5334,7 @@
       </c>
       <c r="N78" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 345 分以上，适合压线求稳或求保底。 ⚠ 2026年院线大幅上调。（该校要点：2026年无锡医学院335，2025年录取9人均分337）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 345 分以上，适合压线求稳或求保底。（该校要点：旧表误把吉林院校标作B区线，已撤销294，2025年录取37人均分336）</t>
         </is>
       </c>
     </row>
@@ -5336,33 +5344,33 @@
       </c>
       <c r="B79" s="20" t="inlineStr">
         <is>
-          <t>吉林</t>
+          <t>青海</t>
         </is>
       </c>
       <c r="C79" s="20" t="inlineStr">
         <is>
-          <t>延吉</t>
+          <t>西宁</t>
         </is>
       </c>
       <c r="D79" s="21" t="inlineStr">
         <is>
-          <t>延边大学</t>
+          <t>青海大学</t>
         </is>
       </c>
       <c r="E79" s="20" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>211/B区</t>
         </is>
       </c>
       <c r="F79" s="20" t="n"/>
       <c r="G79" s="20" t="n">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="H79" s="20" t="n">
         <v>336</v>
       </c>
       <c r="I79" s="20" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="J79" s="20" t="inlineStr">
         <is>
@@ -5386,7 +5394,7 @@
       </c>
       <c r="N79" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 345 分以上，适合压线求稳或求保底。（该校要点：2025年录取37人均分336）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 345 分以上，适合压线求稳或求保底。（该校要点：2025年录取17人均分333）</t>
         </is>
       </c>
     </row>
@@ -5396,33 +5404,31 @@
       </c>
       <c r="B80" s="20" t="inlineStr">
         <is>
-          <t>青海</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C80" s="20" t="inlineStr">
         <is>
-          <t>西宁</t>
+          <t>长沙</t>
         </is>
       </c>
       <c r="D80" s="21" t="inlineStr">
         <is>
-          <t>青海大学</t>
+          <t>湖南师范大学</t>
         </is>
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>211/B区</t>
+          <t>211</t>
         </is>
       </c>
       <c r="F80" s="20" t="n"/>
-      <c r="G80" s="20" t="n">
-        <v>291</v>
-      </c>
+      <c r="G80" s="20" t="n"/>
       <c r="H80" s="20" t="n">
         <v>336</v>
       </c>
       <c r="I80" s="20" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="J80" s="20" t="inlineStr">
         <is>
@@ -5446,7 +5452,7 @@
       </c>
       <c r="N80" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 345 分以上，适合压线求稳或求保底。（该校要点：2025年录取17人均分333）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 345 分以上，适合压线求稳或求保底。（该校要点：2025年录取7人均分336）</t>
         </is>
       </c>
     </row>
@@ -5456,31 +5462,33 @@
       </c>
       <c r="B81" s="20" t="inlineStr">
         <is>
-          <t>湖南</t>
+          <t>福建</t>
         </is>
       </c>
       <c r="C81" s="20" t="inlineStr">
         <is>
-          <t>长沙</t>
+          <t>厦门</t>
         </is>
       </c>
       <c r="D81" s="21" t="inlineStr">
         <is>
-          <t>湖南师范大学</t>
+          <t>厦门大学</t>
         </is>
       </c>
       <c r="E81" s="20" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>985</t>
         </is>
       </c>
       <c r="F81" s="20" t="n"/>
-      <c r="G81" s="20" t="n"/>
+      <c r="G81" s="20" t="n">
+        <v>304</v>
+      </c>
       <c r="H81" s="20" t="n">
         <v>336</v>
       </c>
       <c r="I81" s="20" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J81" s="20" t="inlineStr">
         <is>
@@ -5504,7 +5512,7 @@
       </c>
       <c r="N81" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 345 分以上，适合压线求稳或求保底。（该校要点：2025年录取7人均分336）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 345 分以上，适合压线求稳或求保底。 ⚠ 年录取≤5人，名额极少。（该校要点：2025年录取3人均分336）</t>
         </is>
       </c>
     </row>
@@ -5514,33 +5522,33 @@
       </c>
       <c r="B82" s="20" t="inlineStr">
         <is>
-          <t>福建</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C82" s="20" t="inlineStr">
         <is>
-          <t>厦门</t>
+          <t>呼和浩特</t>
         </is>
       </c>
       <c r="D82" s="21" t="inlineStr">
         <is>
-          <t>厦门大学</t>
+          <t>内蒙古医科大学</t>
         </is>
       </c>
       <c r="E82" s="20" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>B区省属</t>
         </is>
       </c>
       <c r="F82" s="20" t="n"/>
       <c r="G82" s="20" t="n">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="H82" s="20" t="n">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="I82" s="20" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="J82" s="20" t="inlineStr">
         <is>
@@ -5564,7 +5572,7 @@
       </c>
       <c r="N82" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 345 分以上，适合压线求稳或求保底。 ⚠ 年录取≤5人，名额极少。（该校要点：2025年录取3人均分336）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 345 分以上，适合压线求稳或求保底。（该校要点：2025年录取43人均分335，2026年一临录取5人均分330）</t>
         </is>
       </c>
     </row>
@@ -5574,33 +5582,33 @@
       </c>
       <c r="B83" s="20" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C83" s="20" t="inlineStr">
         <is>
-          <t>呼和浩特</t>
+          <t>芜湖</t>
         </is>
       </c>
       <c r="D83" s="21" t="inlineStr">
         <is>
-          <t>内蒙古医科大学</t>
+          <t>皖南医学院</t>
         </is>
       </c>
       <c r="E83" s="20" t="inlineStr">
         <is>
-          <t>B区省属</t>
+          <t>省属</t>
         </is>
       </c>
       <c r="F83" s="20" t="n"/>
       <c r="G83" s="20" t="n">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="H83" s="20" t="n">
         <v>335</v>
       </c>
       <c r="I83" s="20" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J83" s="20" t="inlineStr">
         <is>
@@ -5624,7 +5632,7 @@
       </c>
       <c r="N83" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 345 分以上，适合压线求稳或求保底。（该校要点：2025年录取43人均分335，2026年一临录取5人均分330）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 345 分以上，适合压线求稳或求保底。（该校要点：2025年录取42人均分335）</t>
         </is>
       </c>
     </row>
@@ -5634,33 +5642,31 @@
       </c>
       <c r="B84" s="20" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C84" s="20" t="inlineStr">
         <is>
-          <t>芜湖</t>
+          <t>兰州</t>
         </is>
       </c>
       <c r="D84" s="21" t="inlineStr">
         <is>
-          <t>皖南医学院</t>
+          <t>甘肃中医药大学</t>
         </is>
       </c>
       <c r="E84" s="20" t="inlineStr">
         <is>
-          <t>省属</t>
+          <t>B区省属</t>
         </is>
       </c>
       <c r="F84" s="20" t="n"/>
-      <c r="G84" s="20" t="n">
-        <v>304</v>
-      </c>
+      <c r="G84" s="20" t="n"/>
       <c r="H84" s="20" t="n">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="I84" s="20" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="J84" s="20" t="inlineStr">
         <is>
@@ -5684,7 +5690,7 @@
       </c>
       <c r="N84" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 345 分以上，适合压线求稳或求保底。（该校要点：2025年录取42人均分335）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 340 分以上，适合压线求稳或求保底。（该校要点：—）</t>
         </is>
       </c>
     </row>
@@ -5694,31 +5700,35 @@
       </c>
       <c r="B85" s="20" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C85" s="20" t="inlineStr">
         <is>
-          <t>兰州</t>
+          <t>扬州</t>
         </is>
       </c>
       <c r="D85" s="21" t="inlineStr">
         <is>
-          <t>甘肃中医药大学</t>
+          <t>扬州大学</t>
         </is>
       </c>
       <c r="E85" s="20" t="inlineStr">
         <is>
-          <t>B区省属</t>
-        </is>
-      </c>
-      <c r="F85" s="20" t="n"/>
-      <c r="G85" s="20" t="n"/>
+          <t>省属</t>
+        </is>
+      </c>
+      <c r="F85" s="20" t="n">
+        <v>294</v>
+      </c>
+      <c r="G85" s="20" t="n">
+        <v>299</v>
+      </c>
       <c r="H85" s="20" t="n">
         <v>333</v>
       </c>
       <c r="I85" s="20" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J85" s="20" t="inlineStr">
         <is>
@@ -5742,7 +5752,7 @@
       </c>
       <c r="N85" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 340 分以上，适合压线求稳或求保底。（该校要点：—）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 340 分以上，适合压线求稳或求保底。（该校要点：2025年录取8人均分333）</t>
         </is>
       </c>
     </row>
@@ -5752,17 +5762,17 @@
       </c>
       <c r="B86" s="20" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>辽宁</t>
         </is>
       </c>
       <c r="C86" s="20" t="inlineStr">
         <is>
-          <t>扬州</t>
+          <t>锦州</t>
         </is>
       </c>
       <c r="D86" s="21" t="inlineStr">
         <is>
-          <t>扬州大学</t>
+          <t>锦州医科大学</t>
         </is>
       </c>
       <c r="E86" s="20" t="inlineStr">
@@ -5770,17 +5780,15 @@
           <t>省属</t>
         </is>
       </c>
-      <c r="F86" s="20" t="n">
-        <v>294</v>
-      </c>
+      <c r="F86" s="20" t="n"/>
       <c r="G86" s="20" t="n">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="H86" s="20" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I86" s="20" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="J86" s="20" t="inlineStr">
         <is>
@@ -5804,7 +5812,7 @@
       </c>
       <c r="N86" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 340 分以上，适合压线求稳或求保底。（该校要点：2025年录取8人均分333）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 340 分以上，适合压线求稳或求保底。（该校要点：2025年录取42人均分332）</t>
         </is>
       </c>
     </row>
@@ -5814,17 +5822,17 @@
       </c>
       <c r="B87" s="20" t="inlineStr">
         <is>
-          <t>辽宁</t>
+          <t>山西</t>
         </is>
       </c>
       <c r="C87" s="20" t="inlineStr">
         <is>
-          <t>锦州</t>
+          <t>长治</t>
         </is>
       </c>
       <c r="D87" s="21" t="inlineStr">
         <is>
-          <t>锦州医科大学</t>
+          <t>长治医学院</t>
         </is>
       </c>
       <c r="E87" s="20" t="inlineStr">
@@ -5833,14 +5841,12 @@
         </is>
       </c>
       <c r="F87" s="20" t="n"/>
-      <c r="G87" s="20" t="n">
-        <v>307</v>
-      </c>
+      <c r="G87" s="20" t="n"/>
       <c r="H87" s="20" t="n">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="I87" s="20" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="J87" s="20" t="inlineStr">
         <is>
@@ -5864,7 +5870,7 @@
       </c>
       <c r="N87" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 340 分以上，适合压线求稳或求保底。（该校要点：2025年录取42人均分332）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 335 分以上，适合压线求稳或求保底。（该校要点：2025年麻醉学自划线304，高于当年国家线11分）</t>
         </is>
       </c>
     </row>
@@ -5874,17 +5880,17 @@
       </c>
       <c r="B88" s="20" t="inlineStr">
         <is>
-          <t>山西</t>
+          <t>云南</t>
         </is>
       </c>
       <c r="C88" s="20" t="inlineStr">
         <is>
-          <t>长治</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="D88" s="21" t="inlineStr">
         <is>
-          <t>长治医学院</t>
+          <t>昆明理工大学</t>
         </is>
       </c>
       <c r="E88" s="20" t="inlineStr">
@@ -5893,12 +5899,14 @@
         </is>
       </c>
       <c r="F88" s="20" t="n"/>
-      <c r="G88" s="20" t="n"/>
+      <c r="G88" s="20" t="n">
+        <v>286</v>
+      </c>
       <c r="H88" s="20" t="n">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I88" s="20" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="J88" s="20" t="inlineStr">
         <is>
@@ -5922,7 +5930,7 @@
       </c>
       <c r="N88" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 335 分以上，适合压线求稳或求保底。（该校要点：2025年麻醉学自划线304，高于当年国家线11分）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 335 分以上，适合压线求稳或求保底。 ⚠ 年录取≤5人，名额极少。（该校要点：2025年录取4人均分325）</t>
         </is>
       </c>
     </row>
@@ -5932,33 +5940,33 @@
       </c>
       <c r="B89" s="20" t="inlineStr">
         <is>
-          <t>云南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C89" s="20" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>乌鲁木齐</t>
         </is>
       </c>
       <c r="D89" s="21" t="inlineStr">
         <is>
-          <t>昆明理工大学</t>
+          <t>新疆医科大学</t>
         </is>
       </c>
       <c r="E89" s="20" t="inlineStr">
         <is>
-          <t>省属</t>
+          <t>B区省属</t>
         </is>
       </c>
       <c r="F89" s="20" t="n"/>
       <c r="G89" s="20" t="n">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="H89" s="20" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I89" s="20" t="n">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="J89" s="20" t="inlineStr">
         <is>
@@ -5982,7 +5990,7 @@
       </c>
       <c r="N89" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 335 分以上，适合压线求稳或求保底。 ⚠ 年录取≤5人，名额极少。（该校要点：2025年录取4人均分325）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 330 分以上，适合压线求稳或求保底。（该校要点：2025年录取62人均分324，2026年一临31人均分325）</t>
         </is>
       </c>
     </row>
@@ -5992,33 +6000,33 @@
       </c>
       <c r="B90" s="20" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C90" s="20" t="inlineStr">
         <is>
-          <t>乌鲁木齐</t>
+          <t>十堰</t>
         </is>
       </c>
       <c r="D90" s="21" t="inlineStr">
         <is>
-          <t>新疆医科大学</t>
+          <t>湖北医药学院</t>
         </is>
       </c>
       <c r="E90" s="20" t="inlineStr">
         <is>
-          <t>B区省属</t>
+          <t>省属</t>
         </is>
       </c>
       <c r="F90" s="20" t="n"/>
       <c r="G90" s="20" t="n">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="H90" s="20" t="n">
         <v>324</v>
       </c>
       <c r="I90" s="20" t="n">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="J90" s="20" t="inlineStr">
         <is>
@@ -6042,7 +6050,7 @@
       </c>
       <c r="N90" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 330 分以上，适合压线求稳或求保底。（该校要点：2025年录取62人均分324，2026年一临31人均分325）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 330 分以上，适合压线求稳或求保底。（该校要点：2025年录取19人均分324）</t>
         </is>
       </c>
     </row>
@@ -6052,33 +6060,31 @@
       </c>
       <c r="B91" s="20" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>西藏</t>
         </is>
       </c>
       <c r="C91" s="20" t="inlineStr">
         <is>
-          <t>十堰</t>
+          <t>拉萨</t>
         </is>
       </c>
       <c r="D91" s="21" t="inlineStr">
         <is>
-          <t>湖北医药学院</t>
+          <t>西藏大学</t>
         </is>
       </c>
       <c r="E91" s="20" t="inlineStr">
         <is>
-          <t>省属</t>
+          <t>211/B区</t>
         </is>
       </c>
       <c r="F91" s="20" t="n"/>
-      <c r="G91" s="20" t="n">
-        <v>295</v>
-      </c>
+      <c r="G91" s="20" t="n"/>
       <c r="H91" s="20" t="n">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="I91" s="20" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="J91" s="20" t="inlineStr">
         <is>
@@ -6102,7 +6108,7 @@
       </c>
       <c r="N91" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 330 分以上，适合压线求稳或求保底。（该校要点：2025年录取19人均分324）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 330 分以上，适合压线求稳或求保底。 ⚠ 年录取≤5人，名额极少。（该校要点：—）</t>
         </is>
       </c>
     </row>
@@ -6112,22 +6118,22 @@
       </c>
       <c r="B92" s="20" t="inlineStr">
         <is>
-          <t>西藏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C92" s="20" t="inlineStr">
         <is>
-          <t>拉萨</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="D92" s="21" t="inlineStr">
         <is>
-          <t>西藏大学</t>
+          <t>广东省心血管病研究所</t>
         </is>
       </c>
       <c r="E92" s="20" t="inlineStr">
         <is>
-          <t>211/B区</t>
+          <t>科研院所</t>
         </is>
       </c>
       <c r="F92" s="20" t="n"/>
@@ -6136,7 +6142,7 @@
         <v>321</v>
       </c>
       <c r="I92" s="20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J92" s="20" t="inlineStr">
         <is>
@@ -6170,31 +6176,31 @@
       </c>
       <c r="B93" s="20" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C93" s="20" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>石河子</t>
         </is>
       </c>
       <c r="D93" s="21" t="inlineStr">
         <is>
-          <t>广东省心血管病研究所</t>
+          <t>石河子大学</t>
         </is>
       </c>
       <c r="E93" s="20" t="inlineStr">
         <is>
-          <t>科研院所</t>
+          <t>211/B区</t>
         </is>
       </c>
       <c r="F93" s="20" t="n"/>
       <c r="G93" s="20" t="n"/>
       <c r="H93" s="20" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I93" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J93" s="20" t="inlineStr">
         <is>
@@ -6218,7 +6224,7 @@
       </c>
       <c r="N93" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 330 分以上，适合压线求稳或求保底。 ⚠ 年录取≤5人，名额极少。（该校要点：—）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 330 分以上，适合压线求稳或求保底。 ⚠ 年录取≤5人，名额极少。（该校要点：2025年录取3人均分320）</t>
         </is>
       </c>
     </row>
@@ -6228,31 +6234,33 @@
       </c>
       <c r="B94" s="20" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C94" s="20" t="inlineStr">
         <is>
-          <t>石河子</t>
+          <t>滨州</t>
         </is>
       </c>
       <c r="D94" s="21" t="inlineStr">
         <is>
-          <t>石河子大学</t>
+          <t>滨州医学院</t>
         </is>
       </c>
       <c r="E94" s="20" t="inlineStr">
         <is>
-          <t>211/B区</t>
+          <t>省属</t>
         </is>
       </c>
       <c r="F94" s="20" t="n"/>
-      <c r="G94" s="20" t="n"/>
+      <c r="G94" s="20" t="n">
+        <v>295</v>
+      </c>
       <c r="H94" s="20" t="n">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="I94" s="20" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="J94" s="20" t="inlineStr">
         <is>
@@ -6276,7 +6284,7 @@
       </c>
       <c r="N94" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 330 分以上，适合压线求稳或求保底。 ⚠ 年录取≤5人，名额极少。（该校要点：2025年录取3人均分320）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 325 分以上，适合压线求稳或求保底。（该校要点：2025年录取18人均分318，全国最低梯队）</t>
         </is>
       </c>
     </row>
@@ -6286,17 +6294,17 @@
       </c>
       <c r="B95" s="20" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C95" s="20" t="inlineStr">
         <is>
-          <t>滨州</t>
+          <t>吉首</t>
         </is>
       </c>
       <c r="D95" s="21" t="inlineStr">
         <is>
-          <t>滨州医学院</t>
+          <t>吉首大学</t>
         </is>
       </c>
       <c r="E95" s="20" t="inlineStr">
@@ -6305,14 +6313,12 @@
         </is>
       </c>
       <c r="F95" s="20" t="n"/>
-      <c r="G95" s="20" t="n">
-        <v>295</v>
-      </c>
+      <c r="G95" s="20" t="n"/>
       <c r="H95" s="20" t="n">
         <v>318</v>
       </c>
       <c r="I95" s="20" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J95" s="20" t="inlineStr">
         <is>
@@ -6336,7 +6342,7 @@
       </c>
       <c r="N95" s="23" t="inlineStr">
         <is>
-          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 325 分以上，适合压线求稳或求保底。（该校要点：2025年录取18人均分318，全国最低梯队）</t>
+          <t>过国家线即有较大机会，多为 B 区院校、省属医学院与非直属附属医院。建议初试目标 325 分以上，适合压线求稳或求保底。（该校要点：2024年105118复试线323）</t>
         </is>
       </c>
     </row>
@@ -6473,7 +6479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M109"/>
+  <dimension ref="A1:N109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6487,8 +6493,9 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="62" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="62" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -6563,10 +6570,15 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>数据年份</t>
+          <t>录取数据年份</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>复试口径年份</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>依据说明</t>
         </is>
@@ -6616,12 +6628,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L4" s="25" t="inlineStr">
+      <c r="L4" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M4" s="25" t="inlineStr">
+      <c r="M4" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="25" t="inlineStr">
         <is>
           <t>2026年统考计划7人</t>
         </is>
@@ -6673,12 +6690,17 @@
           <t>1:1.5</t>
         </is>
       </c>
-      <c r="L5" s="27" t="inlineStr">
+      <c r="L5" s="26" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="M5" s="26" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="M5" s="27" t="inlineStr">
+      <c r="N5" s="27" t="inlineStr">
         <is>
           <t>复试资格按招生计划数的 150% 确定；麻醉统考约 10 人</t>
         </is>
@@ -6728,12 +6750,17 @@
           <t>1:1.3</t>
         </is>
       </c>
-      <c r="L6" s="27" t="inlineStr">
+      <c r="L6" s="26" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M6" s="27" t="inlineStr">
+      <c r="M6" s="26" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="N6" s="27" t="inlineStr">
         <is>
           <t>专硕进入复试约 13 人，实际录取 10 人</t>
         </is>
@@ -6783,12 +6810,17 @@
           <t>1:1.3</t>
         </is>
       </c>
-      <c r="L7" s="27" t="inlineStr">
+      <c r="L7" s="26" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M7" s="27" t="inlineStr">
+      <c r="M7" s="26" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="N7" s="27" t="inlineStr">
         <is>
           <t>麻醉学院专硕计划 26 人，进入复试约 34 人，实际录取 26 人</t>
         </is>
@@ -6838,12 +6870,17 @@
           <t>1:1.2</t>
         </is>
       </c>
-      <c r="L8" s="27" t="inlineStr">
+      <c r="L8" s="26" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="M8" s="26" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="M8" s="27" t="inlineStr">
+      <c r="N8" s="27" t="inlineStr">
         <is>
           <t>按各方向招生计划数的 120% 确定复试名单</t>
         </is>
@@ -6891,12 +6928,17 @@
           <t>≥ 1:1.2</t>
         </is>
       </c>
-      <c r="L9" s="27" t="inlineStr">
+      <c r="L9" s="26" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="M9" s="26" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="M9" s="27" t="inlineStr">
+      <c r="N9" s="27" t="inlineStr">
         <is>
           <t>复试比例不低于 1:1.2，进入复试最低线 322 分（含）</t>
         </is>
@@ -6942,12 +6984,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L10" s="25" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="M10" s="25" t="inlineStr">
+      <c r="L10" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="25" t="inlineStr">
         <is>
           <t>2025年专硕录取13人；2026年专硕计划13人</t>
         </is>
@@ -6999,12 +7046,17 @@
           <t>1:1.5</t>
         </is>
       </c>
-      <c r="L11" s="27" t="inlineStr">
+      <c r="L11" s="26" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="M11" s="26" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="M11" s="27" t="inlineStr">
+      <c r="N11" s="27" t="inlineStr">
         <is>
           <t>按统考招生人数 1:1.5 确定复试名单</t>
         </is>
@@ -7054,12 +7106,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L12" s="25" t="inlineStr">
+      <c r="L12" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M12" s="25" t="inlineStr">
+      <c r="M12" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="25" t="inlineStr">
         <is>
           <t>2026年招生7人；2025年录取8人均分345</t>
         </is>
@@ -7107,12 +7164,17 @@
           <t>约 1:1.4</t>
         </is>
       </c>
-      <c r="L13" s="27" t="inlineStr">
+      <c r="L13" s="26" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="M13" s="26" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="M13" s="27" t="inlineStr">
+      <c r="N13" s="27" t="inlineStr">
         <is>
           <t>麻醉学院专硕计划 80 人（含推免 16），统考约 64 人按 1:1.4 划线</t>
         </is>
@@ -7162,12 +7224,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L14" s="27" t="inlineStr">
+      <c r="L14" s="26" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M14" s="27" t="inlineStr">
+      <c r="M14" s="26" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="N14" s="27" t="inlineStr">
         <is>
           <t>麻醉学报考 15 人、录取 13 人，报录比约 1.15:1</t>
         </is>
@@ -7219,12 +7286,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L15" s="25" t="inlineStr">
+      <c r="L15" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M15" s="25" t="inlineStr">
+      <c r="M15" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="25" t="inlineStr">
         <is>
           <t>2025年录取5人均分356</t>
         </is>
@@ -7274,12 +7346,17 @@
           <t>1:1.5</t>
         </is>
       </c>
-      <c r="L16" s="27" t="inlineStr">
+      <c r="L16" s="26" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="M16" s="26" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="M16" s="27" t="inlineStr">
+      <c r="N16" s="27" t="inlineStr">
         <is>
           <t>第一临床医学院统考 33 人、江西医学院 8 人，均按 1:1.5 确定复试名单</t>
         </is>
@@ -7325,12 +7402,17 @@
           <t>1:1.3</t>
         </is>
       </c>
-      <c r="L17" s="27" t="inlineStr">
+      <c r="L17" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="26" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M17" s="27" t="inlineStr">
+      <c r="N17" s="27" t="inlineStr">
         <is>
           <t>第二临床医学院麻醉学拟招生 7 人，复试名单公示 9 人</t>
         </is>
@@ -7374,12 +7456,17 @@
           <t>≥ 1:1.2</t>
         </is>
       </c>
-      <c r="L18" s="27" t="inlineStr">
+      <c r="L18" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="26" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="M18" s="27" t="inlineStr">
+      <c r="N18" s="27" t="inlineStr">
         <is>
           <t>南华临床学院麻醉学专硕计划 4 人</t>
         </is>
@@ -7429,12 +7516,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L19" s="27" t="inlineStr">
+      <c r="L19" s="26" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M19" s="27" t="inlineStr">
+      <c r="M19" s="26" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="N19" s="27" t="inlineStr">
         <is>
           <t>附属第三医院 105100 麻醉学方向报考 16 人、录取 3 人</t>
         </is>
@@ -7486,12 +7578,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L20" s="25" t="inlineStr">
+      <c r="L20" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M20" s="25" t="inlineStr">
+      <c r="M20" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="25" t="inlineStr">
         <is>
           <t>2026年第三临床医学院294（复试比1:2）；2025年录取14人均分354</t>
         </is>
@@ -7543,12 +7640,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L21" s="25" t="inlineStr">
+      <c r="L21" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M21" s="25" t="inlineStr">
+      <c r="M21" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N21" s="25" t="inlineStr">
         <is>
           <t>2026年麻醉学拟录取最低371、最高438、录取8人；2025年录取7人均分372</t>
         </is>
@@ -7598,12 +7700,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L22" s="25" t="inlineStr">
+      <c r="L22" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M22" s="25" t="inlineStr">
+      <c r="M22" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="25" t="inlineStr">
         <is>
           <t>2026年录取30人均分358（区间295-399）</t>
         </is>
@@ -7655,12 +7762,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L23" s="25" t="inlineStr">
+      <c r="L23" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M23" s="25" t="inlineStr">
+      <c r="M23" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="25" t="inlineStr">
         <is>
           <t>2026年校线330、麻醉学370，招生缩至6人；2025年录取10人均分374</t>
         </is>
@@ -7710,12 +7822,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L24" s="27" t="inlineStr">
+      <c r="L24" s="26" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M24" s="27" t="inlineStr">
+      <c r="M24" s="26" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="N24" s="27" t="inlineStr">
         <is>
           <t>第二临床医学院麻醉学报考 23 人、录取 9 人，复试淘汰率约 60.9%</t>
         </is>
@@ -7765,12 +7882,17 @@
           <t>约 1:1.3</t>
         </is>
       </c>
-      <c r="L25" s="27" t="inlineStr">
+      <c r="L25" s="26" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M25" s="27" t="inlineStr">
+      <c r="M25" s="26" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="N25" s="27" t="inlineStr">
         <is>
           <t>第一临床医学院专硕计划 14 人；第三临床医学院招生 6 人、进入复试约 8 人</t>
         </is>
@@ -7820,12 +7942,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L26" s="25" t="inlineStr">
+      <c r="L26" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M26" s="25" t="inlineStr">
+      <c r="M26" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="25" t="inlineStr">
         <is>
           <t>2025年录取62人均分324；2026年一临31人均分325</t>
         </is>
@@ -7871,14 +7998,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L27" s="25" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="M27" s="25" t="inlineStr">
-        <is>
-          <t>2026年麻醉学统考招生1人</t>
+      <c r="L27" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M27" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N27" s="25" t="inlineStr">
+        <is>
+          <t>2026年105118复试线300，统考招生1人</t>
         </is>
       </c>
     </row>
@@ -7926,12 +8058,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L28" s="25" t="inlineStr">
+      <c r="L28" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M28" s="25" t="inlineStr">
+      <c r="M28" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="25" t="inlineStr">
         <is>
           <t>2025年录取6人均分383，为全国最高梯队</t>
         </is>
@@ -7983,12 +8120,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L29" s="25" t="inlineStr">
+      <c r="L29" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M29" s="25" t="inlineStr">
+      <c r="M29" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="25" t="inlineStr">
         <is>
           <t>2025年录取26人均分380，为西南最高；2026年降至335</t>
         </is>
@@ -8038,12 +8180,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L30" s="25" t="inlineStr">
+      <c r="L30" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M30" s="25" t="inlineStr">
+      <c r="M30" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N30" s="25" t="inlineStr">
         <is>
           <t>医学门类专硕校线，麻醉学按1051执行；实际录取分远高于校线</t>
         </is>
@@ -8093,12 +8240,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L31" s="25" t="inlineStr">
+      <c r="L31" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M31" s="25" t="inlineStr">
+      <c r="M31" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N31" s="25" t="inlineStr">
         <is>
           <t>2025年录取25人均分378，含省医临床学院均分402</t>
         </is>
@@ -8150,12 +8302,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L32" s="25" t="inlineStr">
+      <c r="L32" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M32" s="25" t="inlineStr">
+      <c r="M32" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N32" s="25" t="inlineStr">
         <is>
           <t>2025年录取28人均分375</t>
         </is>
@@ -8207,12 +8364,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L33" s="25" t="inlineStr">
+      <c r="L33" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M33" s="25" t="inlineStr">
+      <c r="M33" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N33" s="25" t="inlineStr">
         <is>
           <t>2025年录取24人均分374；2026年湘雅医院一志愿录取最低约386</t>
         </is>
@@ -8237,7 +8399,9 @@
           <t>电子科技大学</t>
         </is>
       </c>
-      <c r="E34" s="24" t="n"/>
+      <c r="E34" s="24" t="n">
+        <v>305</v>
+      </c>
       <c r="F34" s="24" t="inlineStr">
         <is>
           <t>未公布</t>
@@ -8262,14 +8426,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L34" s="25" t="inlineStr">
+      <c r="L34" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M34" s="25" t="inlineStr">
-        <is>
-          <t>2025年录取10人均分372</t>
+      <c r="M34" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="25" t="inlineStr">
+        <is>
+          <t>105118复试线：2024年365、2025年360、2026年305；2025年录取10人均分372</t>
         </is>
       </c>
     </row>
@@ -8317,12 +8486,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L35" s="25" t="inlineStr">
+      <c r="L35" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M35" s="25" t="inlineStr">
+      <c r="M35" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N35" s="25" t="inlineStr">
         <is>
           <t>2025年录取3人均分372</t>
         </is>
@@ -8347,7 +8521,9 @@
           <t>西南医科大学</t>
         </is>
       </c>
-      <c r="E36" s="24" t="n"/>
+      <c r="E36" s="24" t="n">
+        <v>325</v>
+      </c>
       <c r="F36" s="24" t="inlineStr">
         <is>
           <t>未公布</t>
@@ -8372,14 +8548,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L36" s="25" t="inlineStr">
+      <c r="L36" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M36" s="25" t="inlineStr">
-        <is>
-          <t>2025年录取26人均分371</t>
+      <c r="M36" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N36" s="25" t="inlineStr">
+        <is>
+          <t>105118复试线：2024年306、2025年351、2026年325；2025年录取26人均分371</t>
         </is>
       </c>
     </row>
@@ -8429,12 +8610,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L37" s="25" t="inlineStr">
+      <c r="L37" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M37" s="25" t="inlineStr">
+      <c r="M37" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="25" t="inlineStr">
         <is>
           <t>2025年录取34人均分369；2026年麻醉学院线350</t>
         </is>
@@ -8486,12 +8672,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L38" s="25" t="inlineStr">
+      <c r="L38" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M38" s="25" t="inlineStr">
+      <c r="M38" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N38" s="25" t="inlineStr">
         <is>
           <t>1051专硕校线；2025年瑞金医院麻醉录取1人352</t>
         </is>
@@ -8543,12 +8734,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L39" s="25" t="inlineStr">
+      <c r="L39" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M39" s="25" t="inlineStr">
+      <c r="M39" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N39" s="25" t="inlineStr">
         <is>
           <t>1051专硕校线；2026年齐鲁医院麻醉专硕均分392</t>
         </is>
@@ -8600,12 +8796,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L40" s="25" t="inlineStr">
+      <c r="L40" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M40" s="25" t="inlineStr">
+      <c r="M40" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N40" s="25" t="inlineStr">
         <is>
           <t>2026年为1051校线；2025年录取42人均分363；306单科要求170分</t>
         </is>
@@ -8655,12 +8856,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L41" s="25" t="inlineStr">
+      <c r="L41" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M41" s="25" t="inlineStr">
+      <c r="M41" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N41" s="25" t="inlineStr">
         <is>
           <t>2025年录取44人均分362</t>
         </is>
@@ -8710,12 +8916,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L42" s="25" t="inlineStr">
+      <c r="L42" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M42" s="25" t="inlineStr">
+      <c r="M42" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N42" s="25" t="inlineStr">
         <is>
           <t>2025年录取8人均分362</t>
         </is>
@@ -8765,12 +8976,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L43" s="25" t="inlineStr">
+      <c r="L43" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M43" s="25" t="inlineStr">
+      <c r="M43" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N43" s="25" t="inlineStr">
         <is>
           <t>2025年录取47人均分360</t>
         </is>
@@ -8818,12 +9034,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L44" s="25" t="inlineStr">
+      <c r="L44" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M44" s="25" t="inlineStr">
+      <c r="M44" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N44" s="25" t="inlineStr">
         <is>
           <t>2025年录取4人均分360</t>
         </is>
@@ -8873,12 +9094,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L45" s="25" t="inlineStr">
+      <c r="L45" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M45" s="25" t="inlineStr">
+      <c r="M45" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N45" s="25" t="inlineStr">
         <is>
           <t>2024年录取10人；2025年专硕录取6人，线降29分</t>
         </is>
@@ -8926,12 +9152,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L46" s="25" t="inlineStr">
+      <c r="L46" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M46" s="25" t="inlineStr">
+      <c r="M46" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N46" s="25" t="inlineStr">
         <is>
           <t>2025年录取5人均分354</t>
         </is>
@@ -8981,12 +9212,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L47" s="25" t="inlineStr">
+      <c r="L47" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M47" s="25" t="inlineStr">
+      <c r="M47" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N47" s="25" t="inlineStr">
         <is>
           <t>2025年录取27人均分354</t>
         </is>
@@ -9036,12 +9272,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L48" s="25" t="inlineStr">
+      <c r="L48" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M48" s="25" t="inlineStr">
+      <c r="M48" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N48" s="25" t="inlineStr">
         <is>
           <t>2025年录取31人均分354</t>
         </is>
@@ -9091,12 +9332,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L49" s="25" t="inlineStr">
+      <c r="L49" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M49" s="25" t="inlineStr">
+      <c r="M49" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N49" s="25" t="inlineStr">
         <is>
           <t>2025年录取1人353分</t>
         </is>
@@ -9144,14 +9390,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L50" s="25" t="inlineStr">
+      <c r="L50" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M50" s="25" t="inlineStr">
-        <is>
-          <t>2025年录取18人均分353</t>
+      <c r="M50" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N50" s="25" t="inlineStr">
+        <is>
+          <t>2025年105118复试线323；录取18人均分353</t>
         </is>
       </c>
     </row>
@@ -9199,12 +9450,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L51" s="25" t="inlineStr">
+      <c r="L51" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M51" s="25" t="inlineStr">
+      <c r="M51" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N51" s="25" t="inlineStr">
         <is>
           <t>2025年录取9人均分353</t>
         </is>
@@ -9252,12 +9508,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L52" s="25" t="inlineStr">
+      <c r="L52" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M52" s="25" t="inlineStr">
+      <c r="M52" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N52" s="25" t="inlineStr">
         <is>
           <t>2025年录取22人均分352</t>
         </is>
@@ -9307,12 +9568,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L53" s="25" t="inlineStr">
+      <c r="L53" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M53" s="25" t="inlineStr">
+      <c r="M53" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N53" s="25" t="inlineStr">
         <is>
           <t>2025年录取19人均分352</t>
         </is>
@@ -9362,12 +9628,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L54" s="25" t="inlineStr">
+      <c r="L54" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M54" s="25" t="inlineStr">
+      <c r="M54" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N54" s="25" t="inlineStr">
         <is>
           <t>2025年录取约9人均分356（原表数据不完整）</t>
         </is>
@@ -9401,7 +9672,7 @@
         </is>
       </c>
       <c r="G55" s="24" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H55" s="24" t="n">
         <v>295</v>
@@ -9419,14 +9690,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L55" s="25" t="inlineStr">
+      <c r="L55" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M55" s="25" t="inlineStr">
-        <is>
-          <t>2024年录取9人最低349最高420均分373；2025年录取47人均分351</t>
+      <c r="M55" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N55" s="25" t="inlineStr">
+        <is>
+          <t>105118复试线：2024年345、2025年执行A区线293、2026年350；2025年全校各培养单位合计录取49人</t>
         </is>
       </c>
     </row>
@@ -9472,12 +9748,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L56" s="25" t="inlineStr">
+      <c r="L56" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M56" s="25" t="inlineStr">
+      <c r="M56" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N56" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -9527,12 +9808,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L57" s="25" t="inlineStr">
+      <c r="L57" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M57" s="25" t="inlineStr">
+      <c r="M57" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N57" s="25" t="inlineStr">
         <is>
           <t>2025年录取29人均分349；2026年录取14人均分330</t>
         </is>
@@ -9580,14 +9866,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L58" s="25" t="inlineStr">
+      <c r="L58" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M58" s="25" t="inlineStr">
-        <is>
-          <t>2024年拟录取14人最低332</t>
+      <c r="M58" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N58" s="25" t="inlineStr">
+        <is>
+          <t>105118复试线：2024年332、2025年320</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9928,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L59" s="25" t="inlineStr">
+      <c r="L59" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M59" s="25" t="inlineStr">
+      <c r="M59" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N59" s="25" t="inlineStr">
         <is>
           <t>2025年录取21人均分349；2026年疼痛方向录取6人均分338</t>
         </is>
@@ -9694,12 +9990,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L60" s="25" t="inlineStr">
+      <c r="L60" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M60" s="25" t="inlineStr">
+      <c r="M60" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N60" s="25" t="inlineStr">
         <is>
           <t>2025年录取42人均分349</t>
         </is>
@@ -9749,12 +10050,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L61" s="25" t="inlineStr">
+      <c r="L61" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M61" s="25" t="inlineStr">
+      <c r="M61" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N61" s="25" t="inlineStr">
         <is>
           <t>2024年录取6人均分334.8；2026年录取5人均分335.6</t>
         </is>
@@ -9802,12 +10108,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L62" s="25" t="inlineStr">
+      <c r="L62" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M62" s="25" t="inlineStr">
+      <c r="M62" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N62" s="25" t="inlineStr">
         <is>
           <t>2026年录取2人最低359；2025年录取3人均分344</t>
         </is>
@@ -9857,12 +10168,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L63" s="25" t="inlineStr">
+      <c r="L63" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M63" s="25" t="inlineStr">
+      <c r="M63" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N63" s="25" t="inlineStr">
         <is>
           <t>2025年录取28人均分344</t>
         </is>
@@ -9910,12 +10226,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L64" s="25" t="inlineStr">
+      <c r="L64" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M64" s="25" t="inlineStr">
+      <c r="M64" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N64" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -9965,12 +10286,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L65" s="25" t="inlineStr">
+      <c r="L65" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M65" s="25" t="inlineStr">
+      <c r="M65" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N65" s="25" t="inlineStr">
         <is>
           <t>2025年录取24人均分343</t>
         </is>
@@ -10020,12 +10346,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L66" s="25" t="inlineStr">
+      <c r="L66" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M66" s="25" t="inlineStr">
+      <c r="M66" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N66" s="25" t="inlineStr">
         <is>
           <t>2025年录取14人均分342</t>
         </is>
@@ -10075,12 +10406,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L67" s="25" t="inlineStr">
+      <c r="L67" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M67" s="25" t="inlineStr">
+      <c r="M67" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N67" s="25" t="inlineStr">
         <is>
           <t>2025年录取30人均分342</t>
         </is>
@@ -10130,12 +10466,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L68" s="25" t="inlineStr">
+      <c r="L68" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M68" s="25" t="inlineStr">
+      <c r="M68" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N68" s="25" t="inlineStr">
         <is>
           <t>2025年录取19人均分341</t>
         </is>
@@ -10185,12 +10526,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L69" s="25" t="inlineStr">
+      <c r="L69" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M69" s="25" t="inlineStr">
+      <c r="M69" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="25" t="inlineStr">
         <is>
           <t>2025年录取18人均分341</t>
         </is>
@@ -10240,14 +10586,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L70" s="25" t="inlineStr">
+      <c r="L70" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M70" s="25" t="inlineStr">
-        <is>
-          <t>2026年延安医学院麻醉学307分</t>
+      <c r="M70" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="25" t="inlineStr">
+        <is>
+          <t>105118复试线：2024年304、2025年325、2026年307</t>
         </is>
       </c>
     </row>
@@ -10295,12 +10646,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L71" s="25" t="inlineStr">
+      <c r="L71" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M71" s="25" t="inlineStr">
+      <c r="M71" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="25" t="inlineStr">
         <is>
           <t>2025年录取48人均分340</t>
         </is>
@@ -10348,12 +10704,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L72" s="25" t="inlineStr">
+      <c r="L72" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M72" s="25" t="inlineStr">
+      <c r="M72" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="25" t="inlineStr">
         <is>
           <t>2025年录取15人均分339</t>
         </is>
@@ -10403,12 +10764,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L73" s="25" t="inlineStr">
+      <c r="L73" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M73" s="25" t="inlineStr">
+      <c r="M73" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="25" t="inlineStr">
         <is>
           <t>2025年录取约10人均分335（循国家A线）</t>
         </is>
@@ -10460,14 +10826,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L74" s="25" t="inlineStr">
+      <c r="L74" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M74" s="25" t="inlineStr">
-        <is>
-          <t>2026年无锡医学院335；2025年录取9人均分337</t>
+      <c r="M74" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="25" t="inlineStr">
+        <is>
+          <t>105118复试线：2024年319、2025年310、2026年335；2025年录取9人均分337</t>
         </is>
       </c>
     </row>
@@ -10515,14 +10886,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L75" s="25" t="inlineStr">
+      <c r="L75" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M75" s="25" t="inlineStr">
-        <is>
-          <t>2025年录取37人均分336</t>
+      <c r="M75" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N75" s="25" t="inlineStr">
+        <is>
+          <t>旧表误把吉林院校标作B区线，已撤销294；2025年录取37人均分336</t>
         </is>
       </c>
     </row>
@@ -10570,12 +10946,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L76" s="25" t="inlineStr">
+      <c r="L76" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M76" s="25" t="inlineStr">
+      <c r="M76" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N76" s="25" t="inlineStr">
         <is>
           <t>2025年录取3人均分336</t>
         </is>
@@ -10623,12 +11004,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L77" s="25" t="inlineStr">
+      <c r="L77" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M77" s="25" t="inlineStr">
+      <c r="M77" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N77" s="25" t="inlineStr">
         <is>
           <t>2025年录取7人均分336</t>
         </is>
@@ -10678,12 +11064,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L78" s="25" t="inlineStr">
+      <c r="L78" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M78" s="25" t="inlineStr">
+      <c r="M78" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="25" t="inlineStr">
         <is>
           <t>2025年录取17人均分333</t>
         </is>
@@ -10733,12 +11124,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L79" s="25" t="inlineStr">
+      <c r="L79" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M79" s="25" t="inlineStr">
+      <c r="M79" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="25" t="inlineStr">
         <is>
           <t>2025年录取43人均分335；2026年一临录取5人均分330</t>
         </is>
@@ -10788,12 +11184,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L80" s="25" t="inlineStr">
+      <c r="L80" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M80" s="25" t="inlineStr">
+      <c r="M80" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="25" t="inlineStr">
         <is>
           <t>2025年录取42人均分335</t>
         </is>
@@ -10845,12 +11246,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L81" s="25" t="inlineStr">
+      <c r="L81" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M81" s="25" t="inlineStr">
+      <c r="M81" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="25" t="inlineStr">
         <is>
           <t>2025年录取8人均分333</t>
         </is>
@@ -10898,12 +11304,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L82" s="25" t="inlineStr">
+      <c r="L82" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M82" s="25" t="inlineStr">
+      <c r="M82" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -10953,12 +11364,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L83" s="25" t="inlineStr">
+      <c r="L83" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M83" s="25" t="inlineStr">
+      <c r="M83" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N83" s="25" t="inlineStr">
         <is>
           <t>2025年录取42人均分332</t>
         </is>
@@ -11006,12 +11422,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L84" s="25" t="inlineStr">
+      <c r="L84" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M84" s="25" t="inlineStr">
+      <c r="M84" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N84" s="25" t="inlineStr">
         <is>
           <t>2025年麻醉学自划线304，高于当年国家线11分</t>
         </is>
@@ -11061,12 +11482,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L85" s="25" t="inlineStr">
+      <c r="L85" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M85" s="25" t="inlineStr">
+      <c r="M85" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N85" s="25" t="inlineStr">
         <is>
           <t>2025年录取4人均分325</t>
         </is>
@@ -11116,12 +11542,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L86" s="25" t="inlineStr">
+      <c r="L86" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M86" s="25" t="inlineStr">
+      <c r="M86" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N86" s="25" t="inlineStr">
         <is>
           <t>2025年录取19人均分324</t>
         </is>
@@ -11169,12 +11600,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L87" s="25" t="inlineStr">
+      <c r="L87" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M87" s="25" t="inlineStr">
+      <c r="M87" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N87" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -11222,12 +11658,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L88" s="25" t="inlineStr">
+      <c r="L88" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M88" s="25" t="inlineStr">
+      <c r="M88" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N88" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -11275,12 +11716,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L89" s="25" t="inlineStr">
+      <c r="L89" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M89" s="25" t="inlineStr">
+      <c r="M89" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N89" s="25" t="inlineStr">
         <is>
           <t>2025年录取3人均分320</t>
         </is>
@@ -11330,12 +11776,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L90" s="25" t="inlineStr">
+      <c r="L90" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M90" s="25" t="inlineStr">
+      <c r="M90" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N90" s="25" t="inlineStr">
         <is>
           <t>2025年录取18人均分318，全国最低梯队</t>
         </is>
@@ -11347,17 +11798,17 @@
       </c>
       <c r="B91" s="24" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>湖南</t>
         </is>
       </c>
       <c r="C91" s="24" t="inlineStr">
         <is>
-          <t>百色</t>
+          <t>吉首</t>
         </is>
       </c>
       <c r="D91" s="25" t="inlineStr">
         <is>
-          <t>右江民族医学院</t>
+          <t>吉首大学</t>
         </is>
       </c>
       <c r="E91" s="24" t="n"/>
@@ -11371,7 +11822,7 @@
       </c>
       <c r="H91" s="24" t="n"/>
       <c r="I91" s="24" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J91" s="24" t="inlineStr">
         <is>
@@ -11383,14 +11834,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L91" s="25" t="inlineStr">
+      <c r="L91" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M91" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="M91" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N91" s="25" t="inlineStr">
+        <is>
+          <t>2024年105118复试线323</t>
         </is>
       </c>
     </row>
@@ -11400,17 +11856,17 @@
       </c>
       <c r="B92" s="24" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C92" s="24" t="inlineStr">
         <is>
-          <t>咸阳</t>
+          <t>百色</t>
         </is>
       </c>
       <c r="D92" s="25" t="inlineStr">
         <is>
-          <t>陕西中医药大学</t>
+          <t>右江民族医学院</t>
         </is>
       </c>
       <c r="E92" s="24" t="n"/>
@@ -11420,11 +11876,11 @@
         </is>
       </c>
       <c r="G92" s="24" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H92" s="24" t="n"/>
       <c r="I92" s="24" t="n">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="J92" s="24" t="inlineStr">
         <is>
@@ -11436,14 +11892,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L92" s="25" t="inlineStr">
+      <c r="L92" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M92" s="25" t="inlineStr">
-        <is>
-          <t>2025年麻醉学专硕297分</t>
+      <c r="M92" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N92" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -11453,30 +11914,32 @@
       </c>
       <c r="B93" s="24" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C93" s="24" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>咸阳</t>
         </is>
       </c>
       <c r="D93" s="25" t="inlineStr">
         <is>
-          <t>复旦大学</t>
-        </is>
-      </c>
-      <c r="E93" s="24" t="n">
-        <v>320</v>
-      </c>
+          <t>陕西中医药大学</t>
+        </is>
+      </c>
+      <c r="E93" s="24" t="n"/>
       <c r="F93" s="24" t="inlineStr">
         <is>
           <t>未公布</t>
         </is>
       </c>
-      <c r="G93" s="24" t="n"/>
+      <c r="G93" s="24" t="n">
+        <v>2</v>
+      </c>
       <c r="H93" s="24" t="n"/>
-      <c r="I93" s="24" t="n"/>
+      <c r="I93" s="24" t="n">
+        <v>308</v>
+      </c>
       <c r="J93" s="24" t="inlineStr">
         <is>
           <t>未公布</t>
@@ -11487,14 +11950,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L93" s="25" t="inlineStr">
+      <c r="L93" s="24" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="M93" s="25" t="inlineStr">
-        <is>
-          <t>1051专硕校线；麻醉统招约8人，实际录取远高于校线</t>
+      <c r="M93" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N93" s="25" t="inlineStr">
+        <is>
+          <t>2025年麻醉学专硕297分</t>
         </is>
       </c>
     </row>
@@ -11504,20 +11972,22 @@
       </c>
       <c r="B94" s="24" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C94" s="24" t="inlineStr">
         <is>
-          <t>新乡</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="D94" s="25" t="inlineStr">
         <is>
-          <t>新乡医学院</t>
-        </is>
-      </c>
-      <c r="E94" s="24" t="n"/>
+          <t>复旦大学</t>
+        </is>
+      </c>
+      <c r="E94" s="24" t="n">
+        <v>320</v>
+      </c>
       <c r="F94" s="24" t="inlineStr">
         <is>
           <t>未公布</t>
@@ -11536,14 +12006,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L94" s="25" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="M94" s="25" t="inlineStr">
-        <is>
-          <t>麻醉学专业排名全国第33位</t>
+      <c r="L94" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M94" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N94" s="25" t="inlineStr">
+        <is>
+          <t>1051专硕校线；麻醉统招约8人，实际录取远高于校线</t>
         </is>
       </c>
     </row>
@@ -11553,17 +12028,17 @@
       </c>
       <c r="B95" s="24" t="inlineStr">
         <is>
-          <t>广西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C95" s="24" t="inlineStr">
         <is>
-          <t>南宁</t>
+          <t>新乡</t>
         </is>
       </c>
       <c r="D95" s="25" t="inlineStr">
         <is>
-          <t>广西医科大学</t>
+          <t>新乡医学院</t>
         </is>
       </c>
       <c r="E95" s="24" t="n"/>
@@ -11585,14 +12060,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L95" s="25" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="M95" s="25" t="inlineStr">
-        <is>
-          <t>麻醉学专业排名全国第16位</t>
+      <c r="L95" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M95" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N95" s="25" t="inlineStr">
+        <is>
+          <t>麻醉学专业排名全国第33位</t>
         </is>
       </c>
     </row>
@@ -11602,22 +12082,20 @@
       </c>
       <c r="B96" s="24" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广西</t>
         </is>
       </c>
       <c r="C96" s="24" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>南宁</t>
         </is>
       </c>
       <c r="D96" s="25" t="inlineStr">
         <is>
-          <t>东南大学</t>
-        </is>
-      </c>
-      <c r="E96" s="24" t="n">
-        <v>294</v>
-      </c>
+          <t>广西医科大学</t>
+        </is>
+      </c>
+      <c r="E96" s="24" t="n"/>
       <c r="F96" s="24" t="inlineStr">
         <is>
           <t>未公布</t>
@@ -11636,14 +12114,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L96" s="25" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="M96" s="25" t="inlineStr">
-        <is>
-          <t>2026年医学院麻醉学线294</t>
+      <c r="L96" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M96" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N96" s="25" t="inlineStr">
+        <is>
+          <t>麻醉学专业排名全国第16位</t>
         </is>
       </c>
     </row>
@@ -11687,14 +12170,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="L97" s="25" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="M97" s="25" t="inlineStr">
-        <is>
-          <t>2026年医学院麻醉学线300</t>
+      <c r="L97" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M97" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N97" s="25" t="inlineStr">
+        <is>
+          <t>300为临床医学专业学位校级基本线，不等同于105118院线；报考前须再核对医学院细则</t>
         </is>
       </c>
     </row>
@@ -11826,21 +12314,21 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M97"/>
+  <autoFilter ref="A3:N97"/>
   <mergeCells count="13">
-    <mergeCell ref="B100:M100"/>
-    <mergeCell ref="B103:M103"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="B104:M104"/>
-    <mergeCell ref="B108:M108"/>
-    <mergeCell ref="B107:M107"/>
-    <mergeCell ref="B101:M101"/>
-    <mergeCell ref="B102:M102"/>
-    <mergeCell ref="B106:M106"/>
-    <mergeCell ref="B105:M105"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A99:M99"/>
-    <mergeCell ref="B109:M109"/>
+    <mergeCell ref="B104:N104"/>
+    <mergeCell ref="B107:N107"/>
+    <mergeCell ref="B101:N101"/>
+    <mergeCell ref="B108:N108"/>
+    <mergeCell ref="B102:N102"/>
+    <mergeCell ref="B105:N105"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="B106:N106"/>
+    <mergeCell ref="B100:N100"/>
+    <mergeCell ref="A99:N99"/>
+    <mergeCell ref="B109:N109"/>
+    <mergeCell ref="B103:N103"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12156,7 +12644,7 @@
       </c>
       <c r="B5" s="50" t="inlineStr">
         <is>
-          <t>临床医学（专硕）A 区总分线：2024 年 304 分、2025 年 293 分、2026 年 294 分；B 区分别为 294 / 283 / 284 分左右。</t>
+          <t>教育部A区参考总分：2024年304、2025年293、2026年294；B区分别为294、283、284。国家线只作最低参考，不自动等同于院校或培养单位105118复试线。</t>
         </is>
       </c>
     </row>
@@ -12264,7 +12752,7 @@
       </c>
       <c r="B14" s="50" t="inlineStr">
         <is>
-          <t>各院校研究生院官网复试公告 / 复试录取工作办法 / 拟录取名单公示；研招网国家线；软科中国大学专业排名；第三方考研数据整理（启航考研、新东方在线、路灯考研等）。</t>
+          <t>复试线优先采用院校研究生院/招生网官方公告，并在三年统计表中按院校+年度绑定网址；国家线采用教育部公告；录取分来自拟录取名单或院校录取统计。第三方数据仅作补充并明确标注。</t>
         </is>
       </c>
     </row>
